--- a/Assets/StreamingAssets/Chapter/Chapter4.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFB55AD-870A-49B3-BD0F-C65AF7CFF6AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BBEE1A-1A6E-4EEA-B45F-03AAB52AB82A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="剧情走向" sheetId="1" r:id="rId1"/>
@@ -53,9 +53,6 @@
     <t>转场特效</t>
   </si>
   <si>
-    <t>立绘</t>
-  </si>
-  <si>
     <t>对话框头像</t>
   </si>
   <si>
@@ -63,9 +60,6 @@
   </si>
   <si>
     <t>选项</t>
-  </si>
-  <si>
-    <t>QTE</t>
   </si>
   <si>
     <t>指令</t>
@@ -3261,6 +3255,12 @@
   <si>
     <t>在苏格兰岛事件，我依然记得，我救你时，你的神情。</t>
     <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>立绘层</t>
+  </si>
+  <si>
+    <t>TE. HUD层</t>
   </si>
 </sst>
 </file>
@@ -3744,2922 +3744,2922 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="6" t="s">
+        <v>725</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D2" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="E2" s="12" t="s">
-        <v>197</v>
-      </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D3" s="13"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" s="9" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D4" s="13"/>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I4" s="7"/>
       <c r="L4" s="9" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B5" s="9" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D5" s="13"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="9" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B7" s="9" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B8" s="9" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B9" s="9" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B10" s="9" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D11" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D12" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>198</v>
-      </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D13" s="13"/>
       <c r="I13" s="7"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D14" s="13"/>
       <c r="I14" s="7"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D15" s="13"/>
       <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D19" s="13"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D20" s="13"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D21" s="13"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D22" s="13"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D23" s="13"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D24" s="13"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D25" s="13"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D26" s="13"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D27" s="13"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>452</v>
-      </c>
-      <c r="D29" s="14" t="s">
+      <c r="F29" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F29" t="s">
-        <v>15</v>
-      </c>
       <c r="L29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>30</v>
-      </c>
       <c r="F30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F34" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B35" t="s">
+      <c r="F35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" t="s">
         <v>35</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F36" t="s">
+        <v>16</v>
+      </c>
+      <c r="K36" t="s">
         <v>38</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F36" t="s">
-        <v>18</v>
-      </c>
-      <c r="K36" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I37" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D46" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F46" t="s">
+        <v>55</v>
+      </c>
+      <c r="L46" t="s">
         <v>56</v>
-      </c>
-      <c r="F46" t="s">
-        <v>57</v>
-      </c>
-      <c r="L46" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B47" s="9" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B48" s="9" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C48" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F48" t="s">
+        <v>16</v>
+      </c>
+      <c r="L48" t="s">
         <v>59</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F48" t="s">
-        <v>18</v>
-      </c>
-      <c r="L48" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B49" s="9" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F49" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L49" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B50" s="9" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B51" s="9" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B52" s="9" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B53" s="9" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B54" s="9" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L55" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L56" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I57" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K57" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L57" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B59" t="s">
+        <v>66</v>
+      </c>
+      <c r="I59" t="s">
+        <v>67</v>
+      </c>
+      <c r="L59" t="s">
         <v>68</v>
-      </c>
-      <c r="I59" t="s">
-        <v>69</v>
-      </c>
-      <c r="L59" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L62" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B64" t="s">
+        <v>73</v>
+      </c>
+      <c r="I64" t="s">
+        <v>74</v>
+      </c>
+      <c r="L64" t="s">
         <v>75</v>
-      </c>
-      <c r="I64" t="s">
-        <v>76</v>
-      </c>
-      <c r="L64" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L65" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B67" t="s">
+        <v>77</v>
+      </c>
+      <c r="I67" t="s">
+        <v>78</v>
+      </c>
+      <c r="L67" t="s">
         <v>79</v>
-      </c>
-      <c r="I67" t="s">
-        <v>80</v>
-      </c>
-      <c r="L67" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L69" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B71" t="s">
+        <v>82</v>
+      </c>
+      <c r="I71" t="s">
+        <v>83</v>
+      </c>
+      <c r="L71" t="s">
         <v>84</v>
-      </c>
-      <c r="I71" t="s">
-        <v>85</v>
-      </c>
-      <c r="L71" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B73" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L74" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B76" t="s">
+        <v>88</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="I76" t="s">
         <v>90</v>
       </c>
-      <c r="C76" s="10" t="s">
+      <c r="L76" t="s">
         <v>91</v>
-      </c>
-      <c r="I76" t="s">
-        <v>92</v>
-      </c>
-      <c r="L76" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B77" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B78" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L78" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B80" s="9" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I80" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I82" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B83" s="9" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B84" s="9" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B85" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B88" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B89" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L90" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B91" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F91" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L91" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B92" s="9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B94" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B100" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L102" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B103" t="s">
         <v>105</v>
-      </c>
-      <c r="B103" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B104" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B109" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="11" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B114" t="s">
+        <v>107</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E114" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="C114" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E114" s="10" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C116" s="12"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C117" s="12"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C118" s="12"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="11" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C119" s="12"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="11" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C120" s="12"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="11" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C121" s="12"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C122" s="12"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C123" s="12"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C124" s="12"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B125" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B126" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F127" s="9" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D131" s="13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B132" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C132" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="D132" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="D132" s="13" t="s">
-        <v>245</v>
-      </c>
       <c r="F132" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B133" s="4" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B134" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C141" s="12"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B147" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E147" s="12" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B148" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D148" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E148" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L148" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B149" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D149" s="13" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E149" s="12" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D150" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F150" s="9" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D151" s="13" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F151" s="9" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D155" s="13" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E155" s="12"/>
       <c r="H155" s="9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" s="11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D156" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E156" s="12"/>
       <c r="F156" s="9" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H156" s="9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D157" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E157" s="12"/>
       <c r="F157" s="9" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B159" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B160" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B161" s="4" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B162" s="4" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C171" s="12" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172" s="11" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C172" s="12" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C173" s="12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A180" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A181" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A185" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A186" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B187" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B188" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C189" s="12" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A190" s="11" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C190" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A191" s="11"/>
       <c r="B191" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A192" s="11"/>
       <c r="B192" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C192" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A193" s="11"/>
       <c r="B193" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C193" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A194" s="11"/>
       <c r="B194" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C194" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A195" s="11"/>
       <c r="B195" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A196" s="11"/>
       <c r="B196" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C196" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A197" s="11"/>
       <c r="B197" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C197" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A198" s="11"/>
       <c r="B198" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C198" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A199" s="11"/>
       <c r="B199" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C199" s="11" t="s">
         <v>310</v>
-      </c>
-      <c r="C199" s="11" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="11"/>
       <c r="B200" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A201" s="11"/>
       <c r="B201" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C201" s="12" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A202" s="11" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C202" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A203" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A204" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A206" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A207" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A208" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A209" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A210" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A212" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C213" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A215" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A216" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A217" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D217" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E217" s="12" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A218" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D218" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E218" s="12" t="s">
+        <v>699</v>
+      </c>
+      <c r="F218" t="s">
         <v>13</v>
       </c>
-      <c r="E218" s="12" t="s">
-        <v>701</v>
-      </c>
-      <c r="F218" t="s">
-        <v>15</v>
-      </c>
       <c r="L218" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B219" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E219" s="12" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A220" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D220" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A221" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D221" s="14" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F221" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A222" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A223" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D223" s="14" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A224" s="11" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C224" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D224" s="14" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F224" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" s="11"/>
       <c r="B225" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A226" s="11"/>
       <c r="B226" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A227" s="11"/>
       <c r="B227" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A228" s="11" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C228" s="12" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A229" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A230" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A234" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A235" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D235" s="14" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D236" s="13" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E236" s="10" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F236" s="9" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239" s="11" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C239" s="12" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240" s="11" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A241" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A242" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A243" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A244" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A245" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A246" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L246" s="9" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B247" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B248" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A249" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A250" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G250" s="9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B251" s="4" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G251" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L251" s="9" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B252" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A253" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A254" s="11" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A255" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A256" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A257" s="11" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A258" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C258" s="12" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="L258" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A259" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B260" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C260" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B261" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C261" s="12" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="L261" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B262" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C262" s="12" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A263" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C263" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A264" s="11" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B264" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C264" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="G264" t="s">
         <v>127</v>
-      </c>
-      <c r="C264" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="G264" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A265" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C265" s="12" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="G265" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A266" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C266" s="12" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A267" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B267" s="4"/>
       <c r="C267" s="12" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A268" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C268" s="12"/>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A269" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C269" s="12" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A270" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G270" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A271" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A272" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A273" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A274" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A275" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C275" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A276" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A277" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A278" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B279" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C279" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B280" s="4" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D280" s="13" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E280" s="10" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B281" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C281" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D281" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="C281" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="D281" s="14" t="s">
-        <v>140</v>
-      </c>
       <c r="E281" s="10" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="F281" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B282" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C282" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D282" s="14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E282" s="10" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F282" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B283" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A284" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A285" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A286" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B286" s="4"/>
       <c r="K286" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A287" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D287" s="14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E287" s="10" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="I287" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A288" s="11" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D288" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E288" s="12" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="F288" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289" s="11"/>
       <c r="B289" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C289" s="3"/>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A290" s="11"/>
       <c r="B290" s="4" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C290" s="3"/>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A291" s="11"/>
       <c r="B291" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C291" s="3"/>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292" s="11"/>
       <c r="B292" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C292" s="3"/>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A293" s="11"/>
       <c r="B293" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C293" s="3"/>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A294" s="11" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C294" s="3"/>
       <c r="D294" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E294" s="12" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A295" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D295" s="14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E295" s="10" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F295" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B296" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C296" s="10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B297" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B298" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A299" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A300" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A301" s="11" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D301" s="13" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A302" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E302" s="12" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B303" s="4" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C303" s="12" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D303" s="13" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E303" s="12" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F303" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A304" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C304" s="12" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D304" s="13" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E304" s="12" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="I304" s="9"/>
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A305" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C305" s="12"/>
       <c r="D305" s="13"/>
@@ -6668,1019 +6668,1019 @@
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A306" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B306" s="4"/>
       <c r="C306" s="12" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D306" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E306" s="12" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="F306" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A307" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A308" s="11" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A309" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A310" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A311" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C311" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A312" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A313" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L313" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A314" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B314" s="4"/>
       <c r="C314" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L314" s="9" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A315" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A316" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A317" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A318" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E318" s="10" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A319" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C319" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D319" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E319" s="10" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="L319" s="9" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A320" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D320" s="14" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F320" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L320" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A322" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C322" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A323" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A324" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A325" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C325" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B326" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C326" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A327" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C327" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A328" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C328" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B329" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A330" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A331" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A333" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A334" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A335" s="11" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A336" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A337" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D337" s="14" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A338" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D338" s="13" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="F338" s="9" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A339" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A340" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A341" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D341" s="13" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A342" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B342" s="4"/>
       <c r="D342" s="13" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F342" s="9" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A343" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D343" s="13"/>
       <c r="F343" s="9"/>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A344" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D344" s="13" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A345" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D345" s="13" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="F345" s="9" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A346" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A347" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A348" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C348" s="12" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A349" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A350" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A351" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A352" s="11" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A353" s="11" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A354" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A355" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A356" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A357" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A358" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A359" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A360" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A361" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B362" s="4" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A363" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A364" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D364" s="13" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A365" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D365" s="14" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F365" s="9" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B366" s="4" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D366" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F366" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B367" s="4" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="L367" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B368" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L368" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B369" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B370" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B371" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B372" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B373" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A374" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="L374" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A375" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="L375" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A376" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E376" s="12" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A377" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E377" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A378" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E378" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="379" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A379" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="380" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B380" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="L380" s="9" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B381" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D381" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E381" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="382" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B382" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C382" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D382" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E382" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L382" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="383" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B383" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D383" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E383" s="12" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="384" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B384" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="D384" s="13" t="s">
         <v>492</v>
-      </c>
-      <c r="D384" s="13" t="s">
-        <v>494</v>
       </c>
       <c r="E384" s="12"/>
       <c r="F384" s="9" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B385" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="L385" s="9"/>
     </row>
     <row r="386" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A386" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D386" s="13" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="I386" s="9" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="L386" s="9" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A387" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B387" s="4"/>
       <c r="C387" s="12" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D387" s="12" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="L387" s="9" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="388" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A388" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C388" s="12" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D388" s="13" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="I388" s="9" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="L388" s="9" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="389" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A389" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="390" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A390" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="391" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B391" s="4" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B392" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C392" s="12" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="393" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A393" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="394" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A394" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="395" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A395" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D395" s="13"/>
       <c r="I395" s="9"/>
     </row>
     <row r="396" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A396" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C396" s="12" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="I396" s="9"/>
       <c r="L396" s="9"/>
     </row>
     <row r="397" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A397" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D397" s="13" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="398" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A398" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C398" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D398" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F398" s="9" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B399" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C399" s="12"/>
       <c r="D399" s="13"/>
     </row>
     <row r="400" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A400" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F400" s="9"/>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D401" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A402" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D402" s="13" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F402" s="9" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B403" s="4" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B404" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B405" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D405" s="13" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B406" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C406" s="12" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D406" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="E406" s="12" t="s">
+        <v>708</v>
+      </c>
+      <c r="F406" s="9" t="s">
         <v>389</v>
-      </c>
-      <c r="E406" s="12" t="s">
-        <v>710</v>
-      </c>
-      <c r="F406" s="9" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A407" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C407" s="12" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D407" s="13" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E407" s="12" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="F407" s="9" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A408" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A409" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A410" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D410" s="13"/>
       <c r="E410" s="12"/>
@@ -7688,426 +7688,426 @@
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A411" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D411" s="13"/>
       <c r="E411" s="12"/>
       <c r="F411" s="9"/>
       <c r="G411" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B412" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G412" s="9" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B413" s="4" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A414" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A415" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C415" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H415" s="9" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A416" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B416" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B416" s="4" t="s">
-        <v>179</v>
-      </c>
       <c r="C416" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H416" s="9" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A417" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A418" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C418" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H418" s="9" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A419" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C419" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H419" s="9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A420" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A421" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A422" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G422" s="9" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A423" s="11" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G423" s="9" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A424" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C424" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A425" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A426" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A427" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A428" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A429" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A430" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C430" s="10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A431" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A432" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A433" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A434" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A435" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A436" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A437" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A438" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A439" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A440" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A441" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G441" s="9" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A442" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G442" s="9" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A443" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A444" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="G444" s="9" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A445" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C445" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G445" s="9" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A446" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A447" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D447" s="13" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="G447" s="9" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A448" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C448" s="12" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D448" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G448" s="9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="449" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A449" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C449" s="12" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D449" s="13" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E449" s="12" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="G449" s="9" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="450" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A450" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D450" s="13" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E450" s="12" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F450" s="9" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G450" s="9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L450" s="9" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="451" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A451" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D451" s="13"/>
       <c r="E451" s="12"/>
@@ -8116,7 +8116,7 @@
     </row>
     <row r="452" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B452" s="4" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D452" s="13"/>
       <c r="E452" s="12"/>
@@ -8125,10 +8125,10 @@
     </row>
     <row r="453" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A453" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D453" s="13"/>
       <c r="E453" s="12"/>
@@ -8137,363 +8137,363 @@
     </row>
     <row r="454" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A454" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="455" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A455" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="L455" s="9"/>
     </row>
     <row r="456" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A456" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="L456" s="9"/>
     </row>
     <row r="457" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A457" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="L457" s="9"/>
     </row>
     <row r="458" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A458" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="L458" s="9"/>
     </row>
     <row r="459" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A459" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="L459" s="9"/>
     </row>
     <row r="460" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A460" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="L460" s="9"/>
     </row>
     <row r="461" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A461" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="L461" s="9"/>
     </row>
     <row r="462" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A462" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="L462" s="9"/>
     </row>
     <row r="463" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A463" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="L463" s="9"/>
     </row>
     <row r="464" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A464" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="L464" s="9"/>
     </row>
     <row r="465" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A465" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="L465" s="9"/>
     </row>
     <row r="466" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B466" s="4" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="L466" s="9" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="467" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B467" s="4" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="L467" s="9"/>
     </row>
     <row r="468" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A468" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="L468" s="9"/>
     </row>
     <row r="469" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A469" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="L469" s="9"/>
     </row>
     <row r="470" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A470" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="L470" s="9"/>
     </row>
     <row r="471" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A471" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="L471" s="9"/>
     </row>
     <row r="472" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A472" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="L472" s="9"/>
     </row>
     <row r="473" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B473" s="4" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="L473" s="9"/>
     </row>
     <row r="474" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B474" s="4" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="L474" s="9"/>
     </row>
     <row r="475" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A475" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D475" s="13" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="476" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A476" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B476" s="4"/>
       <c r="D476" s="13" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="F476" s="9" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="477" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A477" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="L477" s="9"/>
     </row>
     <row r="478" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A478" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="L478" s="9"/>
     </row>
     <row r="479" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A479" s="11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="L479" s="9"/>
     </row>
     <row r="480" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A480" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="L480" s="9"/>
     </row>
     <row r="481" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B481" s="4" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="L481" s="9"/>
     </row>
     <row r="482" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A482" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C482" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="L482" s="9"/>
     </row>
     <row r="483" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A483" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="L483" s="9"/>
     </row>
     <row r="484" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A484" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="L484" s="9"/>
     </row>
     <row r="485" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B485" s="4" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C485" s="12" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L485" s="9"/>
     </row>
     <row r="486" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B486" s="4" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="L486" s="9"/>
     </row>
     <row r="487" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B487" s="4" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="L487" s="9"/>
     </row>
     <row r="488" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A488" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="L488" s="9"/>
     </row>
     <row r="489" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A489" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="L489" s="9"/>
     </row>
     <row r="490" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A490" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D490" s="13" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="L490" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="491" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A491" s="11"/>
       <c r="B491" s="4" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C491" s="12" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D491" s="13" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F491" s="9" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G491" s="9"/>
       <c r="L491" s="9" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="492" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A492" s="11"/>
       <c r="B492" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="G492" s="9"/>
     </row>
     <row r="493" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A493" s="11"/>
       <c r="B493" s="4" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C493" s="12" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="G493" s="9"/>
       <c r="L493" s="9"/>
@@ -8501,321 +8501,321 @@
     <row r="494" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A494" s="11"/>
       <c r="B494" s="4" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="L494" s="9"/>
     </row>
     <row r="495" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B495" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C495" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D495" s="13" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="496" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B496" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="C496" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="D496" s="13" t="s">
         <v>657</v>
       </c>
-      <c r="C496" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="D496" s="13" t="s">
-        <v>659</v>
-      </c>
       <c r="F496" s="10" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="497" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B497" s="4" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D497" s="13" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="L497" s="9" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="498" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A498" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B498" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D498" s="13" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E498" s="12"/>
       <c r="F498" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L498" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="499" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A499" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B499" s="4" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D499" s="13"/>
     </row>
     <row r="500" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A500" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B500" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D500" s="13"/>
     </row>
     <row r="501" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A501" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B501" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D501" s="13"/>
     </row>
     <row r="502" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A502" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B502" s="4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D502" s="13"/>
       <c r="E502" s="12" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="503" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B503" s="4" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C503" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D503" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E503" s="12" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F503" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L503" s="9" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="504" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B504" s="4" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D504" s="13" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E504" s="12" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F504" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="505" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A505" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B505" s="4" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C505" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="506" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A506" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B506" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="507" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A507" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B507" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C507" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L507" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="508" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A508" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B508" s="4" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="509" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A509" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B509" s="4" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C509" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="510" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B510" s="4" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C510" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="511" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B511" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D511" s="14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="512" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B512" s="4" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D512" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F512" t="s">
         <v>13</v>
       </c>
-      <c r="F512" t="s">
-        <v>15</v>
-      </c>
       <c r="L512" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="513" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B513" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L513" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="514" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A514" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B514" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D514" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L514" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="515" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A515" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B515" s="4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D515" s="13" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="F515" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I515" s="9" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="L515" s="9" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="516" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A516" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B516" s="4"/>
       <c r="C516" s="10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D516" s="13" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="L516" s="9" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="517" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A517" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B517" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="D517" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="F517" t="s">
+        <v>13</v>
+      </c>
+      <c r="I517" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="L517" s="9" t="s">
         <v>719</v>
-      </c>
-      <c r="D517" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="F517" t="s">
-        <v>15</v>
-      </c>
-      <c r="I517" s="9" t="s">
-        <v>720</v>
-      </c>
-      <c r="L517" s="9" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="518" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A518" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B518" s="4" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="F518" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I518" s="9"/>
       <c r="L518" s="9" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="519" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B519" s="4" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="I519" s="9"/>
       <c r="L519" s="9"/>
     </row>
     <row r="520" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L520" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Chapter/Chapter4.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BBEE1A-1A6E-4EEA-B45F-03AAB52AB82A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFB55AD-870A-49B3-BD0F-C65AF7CFF6AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="剧情走向" sheetId="1" r:id="rId1"/>
@@ -53,6 +53,9 @@
     <t>转场特效</t>
   </si>
   <si>
+    <t>立绘</t>
+  </si>
+  <si>
     <t>对话框头像</t>
   </si>
   <si>
@@ -60,6 +63,9 @@
   </si>
   <si>
     <t>选项</t>
+  </si>
+  <si>
+    <t>QTE</t>
   </si>
   <si>
     <t>指令</t>
@@ -3255,12 +3261,6 @@
   <si>
     <t>在苏格兰岛事件，我依然记得，我救你时，你的神情。</t>
     <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>立绘层</t>
-  </si>
-  <si>
-    <t>TE. HUD层</t>
   </si>
 </sst>
 </file>
@@ -3744,2922 +3744,2922 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>724</v>
+        <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>725</v>
+        <v>10</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="13"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" s="9" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D4" s="13"/>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I4" s="7"/>
       <c r="L4" s="9" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B5" s="9" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D5" s="13"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="9" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B7" s="9" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B8" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B9" s="9" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B10" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D13" s="13"/>
       <c r="I13" s="7"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D14" s="13"/>
       <c r="I14" s="7"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D15" s="13"/>
       <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D19" s="13"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D20" s="13"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D21" s="13"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D22" s="13"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D23" s="13"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D24" s="13"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D25" s="13"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D26" s="13"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D27" s="13"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F34" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F35" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F36" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K36" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I37" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F46" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L46" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B47" s="9" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B48" s="9" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F48" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L48" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B49" s="9" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="F49" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B50" s="9" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B51" s="9" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B52" s="9" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B53" s="9" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B54" s="9" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L55" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L56" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I57" t="s">
+        <v>66</v>
+      </c>
+      <c r="K57" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="L57" t="s">
         <v>64</v>
-      </c>
-      <c r="K57" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="L57" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I59" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L59" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L62" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I64" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L64" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L65" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B67" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I67" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L67" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L69" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I71" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L71" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B73" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L74" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I76" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L76" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B77" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L78" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B80" s="9" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="I80" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I82" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B83" s="9" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B84" s="9" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B85" s="9" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B89" t="s">
+        <v>99</v>
+      </c>
+      <c r="C89" s="10" t="s">
         <v>44</v>
-      </c>
-      <c r="B89" t="s">
-        <v>97</v>
-      </c>
-      <c r="C89" s="10" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L90" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B91" s="9" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F91" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L91" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B92" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B94" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L102" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B103" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B109" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="11" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B114" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C116" s="12"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C117" s="12"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C118" s="12"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="11" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C119" s="12"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="11" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C120" s="12"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="11" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C121" s="12"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C122" s="12"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C123" s="12"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C124" s="12"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B125" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B126" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F127" s="9" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D131" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B132" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D132" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F132" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B133" s="4" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B134" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C141" s="12"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B147" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E147" s="12" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B148" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D148" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E148" s="12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L148" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B149" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D149" s="13" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E149" s="12" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D150" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F150" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D151" s="13" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F151" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D155" s="13" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E155" s="12"/>
       <c r="H155" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" s="11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D156" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E156" s="12"/>
       <c r="F156" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H156" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D157" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E157" s="12"/>
       <c r="F157" s="9" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B159" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B160" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B161" s="4" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B162" s="4" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C171" s="12" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172" s="11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C172" s="12" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C173" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A180" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A181" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A185" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A186" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B187" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B188" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C189" s="12" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A190" s="11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C190" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A191" s="11"/>
       <c r="B191" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A192" s="11"/>
       <c r="B192" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C192" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A193" s="11"/>
       <c r="B193" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C193" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A194" s="11"/>
       <c r="B194" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C194" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A195" s="11"/>
       <c r="B195" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A196" s="11"/>
       <c r="B196" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C196" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A197" s="11"/>
       <c r="B197" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C197" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A198" s="11"/>
       <c r="B198" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C198" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A199" s="11"/>
       <c r="B199" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C199" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="11"/>
       <c r="B200" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A201" s="11"/>
       <c r="B201" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C201" s="12" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A202" s="11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C202" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A203" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A204" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A206" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A207" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A208" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A209" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A210" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A212" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C213" s="10" t="s">
         <v>44</v>
-      </c>
-      <c r="B213" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="C213" s="10" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A215" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A216" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A217" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D217" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E217" s="12" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A218" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D218" s="14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E218" s="12" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F218" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L218" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B219" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E219" s="12" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A220" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D220" s="14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A221" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D221" s="14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F221" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A222" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A223" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D223" s="14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A224" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="B224" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="B224" s="4" t="s">
-        <v>319</v>
-      </c>
       <c r="C224" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D224" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F224" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" s="11"/>
       <c r="B225" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A226" s="11"/>
       <c r="B226" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A227" s="11"/>
       <c r="B227" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A228" s="11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C228" s="12" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A229" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A230" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A234" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A235" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D235" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D236" s="13" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E236" s="10" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="F236" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="B239" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="B239" s="4" t="s">
-        <v>333</v>
-      </c>
       <c r="C239" s="12" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240" s="11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A241" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A242" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A243" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A244" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A245" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A246" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="L246" s="9" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B247" s="4" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B248" s="4" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A249" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A250" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G250" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B251" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="G251" t="s">
+        <v>129</v>
+      </c>
+      <c r="L251" s="9" t="s">
         <v>690</v>
-      </c>
-      <c r="G251" t="s">
-        <v>127</v>
-      </c>
-      <c r="L251" s="9" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B252" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A253" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A254" s="11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A255" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A256" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A257" s="11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A258" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C258" s="12" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L258" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A259" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B260" s="4" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C260" s="12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B261" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C261" s="12" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="L261" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B262" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C262" s="12" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A263" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C263" s="12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A264" s="11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C264" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G264" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A265" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C265" s="12" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G265" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A266" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C266" s="12" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A267" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B267" s="4"/>
       <c r="C267" s="12" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A268" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C268" s="12"/>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A269" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C269" s="12" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A270" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G270" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A271" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A272" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A273" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A274" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A275" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C275" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A276" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A277" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A278" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B279" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C279" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B280" s="4" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D280" s="13" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E280" s="10" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B281" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C281" s="10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D281" s="14" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E281" s="10" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="F281" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B282" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C282" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D282" s="14" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E282" s="10" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="F282" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B283" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A284" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A285" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A286" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B286" s="4"/>
       <c r="K286" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A287" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D287" s="14" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E287" s="10" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="I287" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A288" s="11" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D288" s="14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E288" s="12" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="F288" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289" s="11"/>
       <c r="B289" s="4" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C289" s="3"/>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A290" s="11"/>
       <c r="B290" s="4" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C290" s="3"/>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A291" s="11"/>
       <c r="B291" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C291" s="3"/>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292" s="11"/>
       <c r="B292" s="4" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C292" s="3"/>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A293" s="11"/>
       <c r="B293" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C293" s="3"/>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A294" s="11" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C294" s="3"/>
       <c r="D294" s="14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E294" s="12" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A295" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D295" s="14" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E295" s="10" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="F295" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B296" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C296" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B297" s="4" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B298" s="4" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A299" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A300" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A301" s="11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D301" s="13" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A302" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E302" s="12" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B303" s="4" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C303" s="12" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D303" s="13" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E303" s="12" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="F303" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A304" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C304" s="12" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D304" s="13" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E304" s="12" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="I304" s="9"/>
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A305" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C305" s="12"/>
       <c r="D305" s="13"/>
@@ -6668,1019 +6668,1019 @@
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A306" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B306" s="4"/>
       <c r="C306" s="12" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D306" s="14" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E306" s="12" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="F306" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A307" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A308" s="11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A309" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A310" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A311" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C311" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A312" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A313" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L313" s="9" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A314" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B314" s="4"/>
       <c r="C314" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L314" s="9" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A315" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A316" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A317" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A318" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E318" s="10" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A319" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C319" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D319" s="14" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E319" s="10" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="L319" s="9" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A320" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D320" s="14" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F320" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L320" s="9" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A322" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C322" s="10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A323" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A324" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A325" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C325" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B326" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C326" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A327" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C327" s="10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A328" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C328" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B329" s="4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A330" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A331" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A333" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A334" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A335" s="11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A336" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A337" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D337" s="14" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A338" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D338" s="13" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="F338" s="9" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A339" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A340" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A341" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D341" s="13" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A342" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B342" s="4"/>
       <c r="D342" s="13" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F342" s="9" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A343" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D343" s="13"/>
       <c r="F343" s="9"/>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A344" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D344" s="13" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A345" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D345" s="13" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="F345" s="9" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A346" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A347" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A348" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C348" s="12" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A349" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A350" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A351" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A352" s="11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A353" s="11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A354" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A355" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A356" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A357" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A358" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A359" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A360" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A361" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B362" s="4" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A363" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A364" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D364" s="13" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A365" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D365" s="14" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F365" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B366" s="4" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D366" s="14" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F366" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B367" s="4" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="L367" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B368" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L368" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B369" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B370" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B371" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B372" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B373" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A374" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L374" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A375" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L375" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A376" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E376" s="12" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A377" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E377" s="12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A378" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E378" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="379" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A379" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="380" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B380" s="4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L380" s="9" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B381" s="4" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D381" s="14" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E381" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="382" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B382" s="4" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C382" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D382" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E382" s="12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L382" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="383" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B383" s="4" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D383" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E383" s="12" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="384" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B384" s="4" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D384" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E384" s="12"/>
       <c r="F384" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B385" s="4" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L385" s="9"/>
     </row>
     <row r="386" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A386" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D386" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="I386" s="9" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="L386" s="9" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A387" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B387" s="4"/>
       <c r="C387" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D387" s="12" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="L387" s="9" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="388" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A388" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C388" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D388" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="I388" s="9" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="L388" s="9" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="389" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A389" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="390" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A390" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="391" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B391" s="4" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B392" s="4" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C392" s="12" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="393" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A393" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="394" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A394" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="395" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A395" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D395" s="13"/>
       <c r="I395" s="9"/>
     </row>
     <row r="396" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A396" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C396" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I396" s="9"/>
       <c r="L396" s="9"/>
     </row>
     <row r="397" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A397" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D397" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="398" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A398" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C398" s="12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D398" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F398" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B399" s="4" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C399" s="12"/>
       <c r="D399" s="13"/>
     </row>
     <row r="400" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A400" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F400" s="9"/>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D401" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A402" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D402" s="13" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F402" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B403" s="4" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B404" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B405" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D405" s="13" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B406" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C406" s="12" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D406" s="13" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E406" s="12" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="F406" s="9" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A407" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C407" s="12" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D407" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E407" s="12" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="F407" s="9" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A408" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A409" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A410" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D410" s="13"/>
       <c r="E410" s="12"/>
@@ -7688,426 +7688,426 @@
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A411" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D411" s="13"/>
       <c r="E411" s="12"/>
       <c r="F411" s="9"/>
       <c r="G411" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B412" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G412" s="9" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B413" s="4" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A414" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A415" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C415" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H415" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A416" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C416" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H416" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A417" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A418" s="11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C418" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H418" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A419" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C419" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H419" s="9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A420" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A421" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A422" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G422" s="9" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A423" s="11" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G423" s="9" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A424" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C424" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A425" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A426" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A427" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="B427" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="B427" s="4" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A428" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A429" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A430" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C430" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A431" s="11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A432" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A433" s="11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A434" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A435" s="11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A436" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A437" s="11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A438" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A439" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A440" s="11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A441" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G441" s="9" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A442" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G442" s="9" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A443" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A444" s="11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G444" s="9" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A445" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C445" s="12" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="G445" s="9" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A446" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A447" s="11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D447" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G447" s="9" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A448" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C448" s="12" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D448" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G448" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="449" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A449" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C449" s="12" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D449" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E449" s="12" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="G449" s="9" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="450" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A450" s="11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D450" s="13" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E450" s="12" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F450" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G450" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L450" s="9" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="451" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A451" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D451" s="13"/>
       <c r="E451" s="12"/>
@@ -8116,7 +8116,7 @@
     </row>
     <row r="452" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B452" s="4" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D452" s="13"/>
       <c r="E452" s="12"/>
@@ -8125,10 +8125,10 @@
     </row>
     <row r="453" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A453" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D453" s="13"/>
       <c r="E453" s="12"/>
@@ -8137,363 +8137,363 @@
     </row>
     <row r="454" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A454" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="455" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A455" s="11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="L455" s="9"/>
     </row>
     <row r="456" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A456" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="L456" s="9"/>
     </row>
     <row r="457" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A457" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="L457" s="9"/>
     </row>
     <row r="458" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A458" s="11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="L458" s="9"/>
     </row>
     <row r="459" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A459" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="L459" s="9"/>
     </row>
     <row r="460" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A460" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="L460" s="9"/>
     </row>
     <row r="461" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A461" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L461" s="9"/>
     </row>
     <row r="462" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A462" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="L462" s="9"/>
     </row>
     <row r="463" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A463" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="L463" s="9"/>
     </row>
     <row r="464" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A464" s="11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="L464" s="9"/>
     </row>
     <row r="465" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A465" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L465" s="9"/>
     </row>
     <row r="466" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B466" s="4" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L466" s="9" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="467" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B467" s="4" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="L467" s="9"/>
     </row>
     <row r="468" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A468" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="L468" s="9"/>
     </row>
     <row r="469" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A469" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="L469" s="9"/>
     </row>
     <row r="470" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A470" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L470" s="9"/>
     </row>
     <row r="471" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A471" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="L471" s="9"/>
     </row>
     <row r="472" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A472" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L472" s="9"/>
     </row>
     <row r="473" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B473" s="4" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L473" s="9"/>
     </row>
     <row r="474" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B474" s="4" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="L474" s="9"/>
     </row>
     <row r="475" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A475" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D475" s="13" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="476" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A476" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B476" s="4"/>
       <c r="D476" s="13" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="F476" s="9" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="477" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A477" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="L477" s="9"/>
     </row>
     <row r="478" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A478" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="L478" s="9"/>
     </row>
     <row r="479" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A479" s="11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L479" s="9"/>
     </row>
     <row r="480" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A480" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="L480" s="9"/>
     </row>
     <row r="481" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B481" s="4" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="L481" s="9"/>
     </row>
     <row r="482" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A482" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C482" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L482" s="9"/>
     </row>
     <row r="483" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A483" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="L483" s="9"/>
     </row>
     <row r="484" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A484" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L484" s="9"/>
     </row>
     <row r="485" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B485" s="4" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C485" s="12" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L485" s="9"/>
     </row>
     <row r="486" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B486" s="4" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="L486" s="9"/>
     </row>
     <row r="487" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B487" s="4" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L487" s="9"/>
     </row>
     <row r="488" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A488" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="L488" s="9"/>
     </row>
     <row r="489" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A489" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="L489" s="9"/>
     </row>
     <row r="490" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A490" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D490" s="13" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="L490" s="9" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="491" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A491" s="11"/>
       <c r="B491" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C491" s="12" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D491" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F491" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G491" s="9"/>
       <c r="L491" s="9" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="492" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A492" s="11"/>
       <c r="B492" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="G492" s="9"/>
     </row>
     <row r="493" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A493" s="11"/>
       <c r="B493" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C493" s="12" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G493" s="9"/>
       <c r="L493" s="9"/>
@@ -8501,321 +8501,321 @@
     <row r="494" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A494" s="11"/>
       <c r="B494" s="4" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="L494" s="9"/>
     </row>
     <row r="495" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B495" s="4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C495" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D495" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="496" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B496" s="4" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C496" s="12" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D496" s="13" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="F496" s="10" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="497" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B497" s="4" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D497" s="13" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="L497" s="9" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="498" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A498" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B498" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D498" s="13" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E498" s="12"/>
       <c r="F498" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L498" s="9" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="499" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A499" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B499" s="4" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D499" s="13"/>
     </row>
     <row r="500" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A500" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B500" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D500" s="13"/>
     </row>
     <row r="501" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A501" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B501" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D501" s="13"/>
     </row>
     <row r="502" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A502" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B502" s="4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D502" s="13"/>
       <c r="E502" s="12" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="503" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B503" s="4" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C503" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D503" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E503" s="12" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F503" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L503" s="9" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="504" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B504" s="4" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D504" s="13" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E504" s="12" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F504" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="505" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A505" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B505" s="4" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C505" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="506" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A506" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B506" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="507" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A507" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B507" s="4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C507" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L507" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="508" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A508" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B508" s="4" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="509" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A509" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B509" s="4" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C509" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="510" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B510" s="4" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C510" s="10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="511" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B511" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D511" s="14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="512" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B512" s="4" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="D512" s="14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F512" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L512" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="513" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B513" s="4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L513" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="514" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A514" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B514" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D514" s="14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L514" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="515" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A515" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B515" s="4" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D515" s="13" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="F515" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I515" s="9" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="L515" s="9" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="516" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A516" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B516" s="4"/>
       <c r="C516" s="10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D516" s="13" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="L516" s="9" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="517" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A517" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B517" s="4" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D517" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F517" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I517" s="9" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="L517" s="9" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="518" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A518" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B518" s="4" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="F518" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I518" s="9"/>
       <c r="L518" s="9" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="519" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B519" s="4" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="I519" s="9"/>
       <c r="L519" s="9"/>
     </row>
     <row r="520" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L520" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Chapter/Chapter4.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFB55AD-870A-49B3-BD0F-C65AF7CFF6AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FFF0A2-9A68-4C98-84F7-6DB808875ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="剧情走向" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="746">
   <si>
     <t>人物</t>
   </si>
@@ -83,9 +83,6 @@
     <t>黑场</t>
   </si>
   <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;寒风凛冽，白云细长，小雪渐落，青苔被点上一星星的白。地上的人张开大拇指，便可把黑洞藏住。云雾形成卷云，从万米高空钻入黑洞中。</t>
-  </si>
-  <si>
     <t>音效/风声|音效/车子行驶</t>
   </si>
   <si>
@@ -179,21 +176,12 @@
     <t>收到，请继续。</t>
   </si>
   <si>
-    <t>周文涵的声音带有一丝紧张。</t>
-  </si>
-  <si>
     <t>漠寒将「空间爆破仪」拿出，启动后悬置在光圈中心。仪器响了一声，漠寒松开手，后退两步。</t>
   </si>
   <si>
     <t>音效/滴1|音效/脚步声</t>
   </si>
   <si>
-    <t>仪器快速旋转，并发出狂风般的“嗖嗖”声。恍惚间，漠寒好像感觉有什么东西在撩自己的毛一样。他望向黑洞——黑洞边缘出现一层淡紫色的光，这层光给了漠寒一种强烈的既视感。</t>
-  </si>
-  <si>
-    <t>音效/能量蓄力1</t>
-  </si>
-  <si>
     <t>漠寒打了个寒颤，或许这不是出于寒冷。</t>
   </si>
   <si>
@@ -260,18 +248,12 @@
     <t>goto &gt;&gt; 遗骸-前:全部探索完成检测1</t>
   </si>
   <si>
-    <t>这里的人曾想过抗争——</t>
-  </si>
-  <si>
     <t>广告牌:打破黑洞</t>
   </si>
   <si>
     <t>addTag &gt;&gt; 遗骸:查看广告牌1</t>
   </si>
   <si>
-    <t>但是呢……？</t>
-  </si>
-  <si>
     <t>（逃离地球……？）</t>
   </si>
   <si>
@@ -341,9 +323,6 @@
     <t>背景缩放比例 &gt;&gt; 默认</t>
   </si>
   <si>
-    <t>你……来这里干什么？</t>
-  </si>
-  <si>
     <t>音效/手枪上膛</t>
   </si>
   <si>
@@ -380,24 +359,15 @@
     <t>音效/对讲机噪声</t>
   </si>
   <si>
-    <t>漠寒愤怒地吐出这个名字，额头上出现皱纹，吻部上也因为咬合而出现肉块。</t>
-  </si>
-  <si>
     <t>对讲机里没有谁在说话了，都是些杂乱的脚步声与金属撞击的声音。云叶枫把对讲机调成收音模式，然后交给了漠寒。叶苏明只是往漠寒移了几步。</t>
   </si>
   <si>
-    <t>漠寒，你好像基本不骂人。</t>
-  </si>
-  <si>
     <t>漠寒重重吸了口气……</t>
   </si>
   <si>
     <t>wait &gt;&gt; 5</t>
   </si>
   <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;忽然，三个人停了下来，眼前是一家大型科技企业，企业的正门有一只倒下的企鹅雕塑，企业门牌“TENCENC”一角砸在了地上。大楼的墙户有些已经破碎了，但是框架还算是完美，相对它旁边的建筑，TENCENC大楼的遗骸可以算作是完好的建筑。</t>
-  </si>
-  <si>
     <t>遗骸/废墟-世界泡广告牌</t>
   </si>
   <si>
@@ -431,36 +401,18 @@
     <t>漠寒擦去因龇牙而流下的口水</t>
   </si>
   <si>
-    <t>智商堪忧。</t>
-  </si>
-  <si>
-    <t>(所以这个企业是干什么的？为什么它的规模这么大？)</t>
-  </si>
-  <si>
     <t>这怎么办？</t>
   </si>
   <si>
-    <t>云叶枫巡视周围，偶然间他瞄到了另一个电梯。他走过去按下电梯按钮，发现这个电梯不需要密码。他示意其他两人过来，他们站在电梯前等着，接着，他们听到了“咯吱咯吱”的机械声，电梯门上面的楼层数也在缓缓减小。</t>
-  </si>
-  <si>
-    <t>随着声音越来越大，他们开始警戒，他们后退几步，叶苏明看着后面，其他二人拿枪指着电梯门。“咚”一声后，电梯门缓缓开启，三人的心快跳到了嗓子上。但是里面除了微弱了灯光和地上的血迹之外，没有任何东西了。</t>
-  </si>
-  <si>
     <t>音效/电梯开门1</t>
   </si>
   <si>
-    <t>他示意队员们进电梯，都到齐后，漠寒有些犹豫地按下了带有血迹的按钮。按钮亮起蓝光，电梯门缓缓关闭，接着，他们感觉到自己在上升。电梯中的灯光忽明忽暗，随着楼层数越来越高，他们越来越说不出话，只是感觉嗓子里干燥。</t>
-  </si>
-  <si>
     <t>音效/电梯关门1</t>
   </si>
   <si>
     <t>遗骸/电梯_1</t>
   </si>
   <si>
-    <t>电梯在最顶楼停下，电梯门打开，他们发现这里是实验室。窗外的光散射进实验室，似乎这里刚迎来早晨……</t>
-  </si>
-  <si>
     <t>遗骸/楼顶实验室</t>
   </si>
   <si>
@@ -485,18 +437,9 @@
     <t>遗骸/遗言|Loop</t>
   </si>
   <si>
-    <t>我们可以很直白且郑重地告诉你：这个黑洞绝对不是好东西，尽管它看上去是前途无限，但是我劝你们赶紧把他丢进垃圾桶里面。</t>
-  </si>
-  <si>
-    <t>不过，我们很好奇，很多我们前仆后继对抗黑洞，为什么偏偏是你们恰好可以解决这个黑洞？</t>
-  </si>
-  <si>
     <t>漠寒回头看向云叶枫，发现云叶枫在录制视频，于是放心地点了点头。</t>
   </si>
   <si>
-    <t>视频结束，漠寒走向前观察了一圈U盘，接着拔下了U盘。</t>
-  </si>
-  <si>
     <t>音效/拿放东西1</t>
   </si>
   <si>
@@ -506,9 +449,6 @@
     <t>陈鑫 ·)</t>
   </si>
   <si>
-    <t>炸弹可以爆炸，各组队员注意安全！</t>
-  </si>
-  <si>
     <t>三人</t>
   </si>
   <si>
@@ -612,9 +552,6 @@
   </si>
   <si>
     <t>让开！</t>
-  </si>
-  <si>
-    <t>音效/跑步声|音效/摔倒</t>
   </si>
   <si>
     <t>wait &gt;&gt; 4</t>
@@ -942,18 +879,10 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>语音/遗骸/截止目前...</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>OverTheChapter</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒在越野车里望着窗外，北冰洋的风雪比上次的大，他想了很多东西……</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>——FoxTi小队，空间映射建模已经完成，现在可以跟进任务。</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -962,10 +891,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>他们穿过一排排残破的车辆，漠寒按下电梯门按钮，但是门框弹出一个输入按钮界面的投影。上面写道：“虹膜识别系统损坏，请输入备用密码”。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>我们和他们暂时不是敌人。世界蛇来到这里的目的目前未知，我们不可盲目行动。</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -1058,14 +983,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>他的呼吸中带着一点急促，手指微微颤抖。他的脑子里瞬间闪过一段回忆——有一次漠寒在劝他和一位虎人的架，对面的虎人可不惯着漠寒，和漠寒打得不可开交——</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>这在漠寒的劝架史上还是头一次——当时他因恐惧未能帮忙，每次想到这些类似的事情，他都有一种无力感。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>漠寒</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -1222,10 +1139,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>果然，他感受不到队友的心跳，心彻底沉了下去。他绝望地低吼一声，双手无力垂落。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>None</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -1254,10 +1167,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>不知道！这是误会，对不对？一定是！（抱头嘶吼）他们开枪肯定是因为幻觉！这只是意外——意外！</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>云叶枫只是凝视着他。</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -1266,10 +1175,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>世界蛇成员猛吸一口气，目光重新聚焦，变得异常镇定。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>我明白了……</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -1286,22 +1191,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>他站起身，令云叶枫意外的是，他竟将对讲机递给了自己。云叶枫握紧枪，看着他迈过尸体，掠过漠寒，背起被电晕的队友走向裂缝。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>经过漠寒时，他用有些颤抖的声音轻声说：</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>不是你的错——世界蛇向来对死人不管不顾，除了发放死金，没人关心他们是怎么死的。你们尽可以把尸体藏起来，他们中有些人也乐意死在里面——劝你们……‘早点回家’。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫收好对讲机，快步跑到漠寒身边。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>振作点！</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -1358,10 +1247,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>陈队，我们现在与以钛科学的人对峙，他们劫持了我们一名队员，应该怎——</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>开枪！</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -1370,10 +1255,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>我们早在前面发现以钛科学的踪迹，显然，你们眼前的人是Ω型虚空兽的致幻！</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>但是他们举止很像人类，我们被劫持的队员也还活——</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -1562,14 +1443,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒调侃着，顺便看向手环投影——坐标点还在下面。他们一起检查了一下四周的安全情况，发现没有危险因素后，漠寒左右环望，发现绿光下隐约有一扇电梯门，除此之外，没有别的路了。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>你好，下一个世界的人。我是制造这个世界的科学家之一——杨奇。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>杨奇 ·）</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -1642,10 +1515,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒……？</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>叶苏明白点不安地说道。</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -1682,10 +1551,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>他感觉周遭的黑暗是粘稠的，像化不开的墨汁，将每一寸空气都染成了沉郁的黑。这里没有星光，没有月色，好似它从未存在。黑暗在慢慢漫上来，从脚边开始，沿着脚踝，爬上膝盖，像冰冷的潮水，无声无息地漫过胸口。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>有什么东西在下沉，不是身体，而是意识里最后一点光亮。它坠着，坠着，朝着那片更深更静的地方去，那里没有上下左右，只有一种永恒的、无需呼吸的安宁。</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -1710,10 +1575,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒，你开门后灯就黑了，但你人不见，还联系不上。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>叶苏明 ·)</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -1842,27 +1703,11 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒眼睁睁地看见空间闭合，但是自己却移动不了。他拉开口袋，把捡来的U盘丢出了空间裂缝外，在云叶枫蓄力好的那一刻，空间裂缝瞬间闭合……</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>&lt;中心文本&gt;&lt;淡入&gt;他脚下站着的地面裂开，好像一张巨口，无情地吞噬了他。他飘在空中，眼睛盯着那正在逐渐破碎的黑洞。耳旁是冰冷且喧嚣的风，在为他的死亡做伴奏。他转头看向身下的虚空，惊奇地发现一块真正溶解的粒子核心，他猜测这是这块地方重力的来源。</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;核心突然爆炸，一股力量推着他上升。朦胧中，他看见一个踏空而来的紫色影子，是个龙人，提着紫色长剑缓缓走近。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动延时 &gt;&gt; 6|wait &gt;&gt; 3|addTag &gt;&gt; 解锁第四章</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>&lt;中心文本&gt;○ Position: The Arctic Ocean</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/车子行驶而过|语音/遗骸/此以钛事件...</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
@@ -2243,10 +2088,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>他他妈要干些什么逼事情？</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>陈鑫？你指的是？</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -2255,14 +2096,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒回答，字里行间中带着不解与愤恨。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>没事，我太激动了。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>音效/金属挤压变形1</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -2319,10 +2152,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>&lt;size=48&gt;&lt;b&gt;你妈的陈鑫！</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>三人停了下来，眼前是一扇生锈的铁门，铁门上用血写着“YOU SHOULDN'T COME HERE”。</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -2415,18 +2244,10 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>嘘......</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>addTag &gt;&gt; 解锁第五章</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>自动延时 &gt;&gt; 12.5|wait &gt;&gt; 3</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>单点 &gt;&gt; ▲ &gt;&gt; 前往 &gt;&gt; 裂缝外1 &gt;&gt; 0 &gt;&gt; -100 &gt;&gt; 0.75</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -2467,10 +2288,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>三人这时候才意识到，黑洞的引力变大了。光圈被快速填充，发散出五彩斑斓的白。随后它快速扩大，反复拉伸，形成一块破损的巨幕。三人都愣住了——他们头一次见这么大的空间裂缝。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>漠寒走了进去，被脚底下有形而看不见的空间绊了一跤，抬头后发现自己来了一个破旧的城市之中。</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -2563,58 +2380,14 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>换句话说，这个黑洞已经被我们处理地危害最小了……我们可以留下的话不多，但是我们很多数据全部都留在了U盘里面。拿走吧！祝你们好运——</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>就我们所知，没有一个世界是可以驾驭住这个黑洞的。据我猜测，它或许曾是某种星际级武器……</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>突然，漠寒发现原先插U盘的地方露出来了什么东西，漠寒将其扯出，发现是一张纸，纸上写着：</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>备用密码：World Bubble</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒思索着，他记得输入界面中没有提供英文字母的按键。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明凑过来，拿过漠寒手中的纸条，瞪眼看着</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>23……15……18……12、4、2……21、22、12、5。嗯23151812422122125。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒和云叶枫对视一眼，将信将疑。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明，你是怎么把密码推出来的？</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>三人在实验室看了一圈，发现没有什么特别的东西，于是乘坐电梯再次回到停车场。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒皱着眉头来到电梯按钮旁边，输入密码，电梯门缓缓打开。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>遗骸/楼顶实验室</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>音效/电梯开门1|音效/跑步声</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>音效/滴1|音效/电梯开门1</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -2623,26 +2396,10 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>我肏，牛逼啊。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>啊……（不好意思地看向漠寒）上次和漠寒玩恐怖游戏解密的时候，有这样类似的解密——只不过故意告诉了漠寒错误的密码。然后……</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>然后我就被鬼突脸了。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>云叶枫刚要笑，漠寒腰上的无线对讲机传来噪声。一会儿后，陈鑫的声音传来：</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>什么鬼？谁家电梯要密码的？</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>嗯……这里的人类有创造世界泡的技术？</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -2651,14 +2408,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>现在，我将用我的语言为这个世界送行，也为前来这个世界的人类留下我们的祝福和信息。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>想必，你们的世界中也出现了一个黑洞，对吧？这和我们很像。我们打算像之前的世界一样，如果被这个黑洞毁灭，那就留下遗言警示后人。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>好在乘电梯的时候没有“特别”的小插曲，电梯平缓到达任务点，三人走出电梯，都松了一口气。</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -3023,14 +2772,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>云叶枫和叶苏明冲出去，在裂缝的另一边后退一个身位等待漠寒冲出来。但是漠寒刚走一步，中弹的大腿开始剧痛——这个剧痛让他直接跪下了。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明见漠寒这个样子，刚打算冲进来，云叶枫不打算拦，但是看到空间有迅速闭合的征兆后迅速拉住了叶苏明，把戴了手套的一只手对准漠寒——他想用手套把漠寒拉过来。</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>&lt;b&gt;&lt;size=48&gt;别提她！</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -3051,10 +2792,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>&lt;淡入&gt;&lt;中心文本&gt;未完待续......</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>&lt;淡入&gt;&lt;中心文本&gt;感谢您游玩什纳Demo&lt;br&gt;&lt;size=18&gt;&lt;再次点击返回至主菜单&gt;</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -3260,6 +2997,370 @@
   </si>
   <si>
     <t>在苏格兰岛事件，我依然记得，我救你时，你的神情。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>addTag &gt;&gt; 解锁第四章</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒风凛冽，白云细长，小雪渐落，青苔被点上一星星的白。云在天上卷着，像是乱麻。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>来这里干什么？</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>老大……？</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>老大，你开门后灯就黑了，但你人不见，还联系不上。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>仪器快速旋转，并发出狂风般的“嗖嗖”声。恍惚间，漠寒好像感觉有什么东西在撩自己的毛一样。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>光圈被快速填充，发散出五彩斑斓的白。随后它快速扩大，反复拉伸，形成一块破损的巨幕。三人都愣住了——他们头一次见这么大的空间裂缝。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>我以为我做好了准备，可是这场景……</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫缓缓拿出相机，呼吸都变得凝滞</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>今天先导探测组（数据分析组，根据裂缝数据分析内在空间情况，并投入机器人粗略探测）说的没错，这……真是平行世界！</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>远处一些细小的灰尘被黑洞吸起吞入。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们不会被黑洞吃掉吧？</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>先导探测组不是说过‘这是一个拟似黑洞，引力连老鼠都吸不起来’，更何况我们——</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>别立flag，我怕好吧……</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里的人曾想过抗争——</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>但是呢……？</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>他的呼吸中带着一点急促，手指微微颤抖，有一种无力感。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>果然，他感受不到队友的心跳，心彻底沉了下去。他绝望地坐着，双手无力垂落。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>这是误会，对不对？</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界蛇成员猛吸一口气，目光重新聚焦。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>他站起身，令云叶枫意外的是，他竟将对讲机递给了自己。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫握紧枪，看着他迈过尸体，走向漠寒，叶苏明谨慎地盯着这名队员，做好了战斗的准备。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>副队。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>这名队员摘下头盔，漠寒瞳孔收缩——是文森。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>不是你的错——你也知道，世界蛇向来对死人不管不顾，除了发放死金，没人关心他们是怎么死的。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>你们尽可以把尸体藏起来，他们中有些人也乐意死在里面——劝你们……‘早点回家’。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>他略过漠寒，背起被电晕的队友走向裂缝，</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>当时你劝我转行，我还在犹豫。你的建议是对的，毕竟，你也这么做了，对吧？</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫收好对讲机，快步跑到漠寒身边，内心感叹漠寒的关系网的广泛。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈队，我们现在与以钛科学的人对峙，一个人类，两名兽人——一个长得像之前的副队，他们劫持了我们一名队员，应该怎——</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们早在前面发现以钛科学的踪迹，显然，你们眼前的人是Ω型虚空兽的致幻！更别提他，他连工作找到没都不知道！</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈鑫？</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒眉头微蹙，眼神呆滞，突然，原本松弛的面部肌肉突然紧绷，嘴巴微张，身体不自觉地后退半步</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>为什么是他？</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪不得……</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒嘴角浮起一丝苦笑</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>老大？</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>没事。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;忽然，三个人停了下来，眼前是一家大型科技企业，企业的正门有个几米高的兽人雕塑，企业门牌“TENCENC”一角砸在了地上。大楼的墙户有些已经破碎了，但是框架还算是完美，相对它旁边的建筑，TENCENC大楼的遗骸可以算作是完好的建筑。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>他们走到雕塑下，开始观察这个雕塑，这是一个狼人雕塑，英姿飒爽地站在蜂窝结构似的底座上，抬头望向远方，满脸坚定。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>狼人穿着科考装备，手上拿着不知道是什么样的容器。底座上写着一段英文，翻译过来是：</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>群星以你而转动。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>雕塑的名字被划痕磨得看不清了，名字又写着“21CE - 16CE”。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘宇轩早在任务前就和我说怀疑这个世界泡是人造的。但是，为什么这里只剩下一片废墟？</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个我知道！烂尾了！</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>呃……或许他们……因为某种原因又离开了这里？</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫双手合十，接着拉开。他的指尖之间出现白色的光丝，掌间淡入他们所处位置的建模投影，</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>随后，云叶枫再次将双手拉开一点点距离，投影的深度增加。他们发现地下有错综的通道，而任务点就在地下的某个区域。三人决定探索向下的路。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>智商堪忧——不过，我们真的遇到了虚空兽，遇到了被认为几乎存在于太阳系内的虚空兽，甚至一模一样。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>说明虚空兽来源于一次大范围的以钛宇宙事件是真的？</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>不，也许我们本土的虚空兽刚刚逸散到这里来的……</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>向指挥部汇报完基本情况，他们一起检查了一下四周的安全情况，发现没有危险因素后，他们穿过一排排残破的车辆，找到了一个电梯，除此之外，没有别的路了。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>(所以这个企业是干什么的？为什么它的规模这么大？)</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>电梯上下的按钮旁还有一个插入槽，漠寒按下电梯门按钮，但是门框弹出一个全息投影。上面写道：“虹膜识别系统损坏，请使用权限”。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>什么鬼？谁家电梯要权限的？</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫巡视周围，偶然间他瞄到了另一个电梯。他走过去按下电梯按钮，发现这个电梯不需要权限。他示意其他两人过来，他们站在电梯前等着，接着，他们听到了“咯吱咯吱”的机械声，电梯门上面的楼层数也在缓缓减小。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>随着声音越来越大，他们开始警戒，他们后退几步，叶苏明看着后面，其他二人拿枪指着电梯门。“咚”一声后，电梯门缓缓开启，三人的心快跳到了嗓子上。但是里面除了微弱了灯光和地上的血迹之外，没有任何东西了。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>他示意队员们进电梯，都到齐后，漠寒有些犹豫地按下了带有血迹的按钮。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>按钮亮起蓝光，电梯门缓缓关闭，接着，他们感觉到自己在上升。电梯中的灯光忽明忽暗，随着楼层数越来越高，他们越来越说不出话，只是感觉嗓子里干燥。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>老大？这层楼按钮上有血诶，真的要去吗？</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯。死也要去那，说明有东西。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>电梯在最顶楼停下，电梯门打开，他们发现这里是实验室。窗外的光散射进实验室，似乎这里刚迎来早晨……</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>你好，群星或者他者。我是制造这个世界的科学家之一——杨奇。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在，根据传统，我将用我的语言为这个世界送行，也为前来这个世界的人类留下我们的祝福和信息。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个黑洞的。据我猜测，它或许曾是某种星际级武器……群星不息，黑潮不止，我们的命运被锁死在了群星里。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>当然，我看到了光。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有一个低级文明是可以驾驭住这个黑洞的，群星中没了回声，而黑洞已经被我们处理得危害最小了。如果它真要重新回到循环的开端，我希望，没有人再去犯傻了！</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们可以留下的话不多，但是我们很多数据全部都留在了U盘里面。拿走吧！祝你们好运——目前所有的权限都下放到了群星象征，方便你们自由通行……</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>视频结束，漠寒走向前观察了一圈U盘，接着拔下了U盘。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>备用群星就在这层楼。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>三人在这层楼逛了几圈，找到一个房间。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个房间是蜂窝风格，房间的中央放着一个展台，展台中央放着一罐巴掌大的液体容器，展台上标注：群星象征。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个容器是直三棱柱式的，容器的底座上有发着橙黄色荧光的海藻似的条带，条带包裹着悬浮在液体中央的像是DNA的双螺旋结构，容器的顶部有一个凸起接口。看样子，这就是杨奇说的群星。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒拿起群星仔细观察，发现这个接口似乎能插入电梯的插入槽。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>于是他们乘坐电梯再次回到停车场。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐/SCP-x6x|音效/滴水声2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒皱着眉头来到电梯按钮旁边，刚刚好插入群星。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>群星弹出，电梯门缓缓打开。漠寒收起群星。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>三人进入电梯。里面很干净，甚至干净得有些过分。这一切，像是为欢迎谁一样。漠寒腰上的无线对讲机突然传出噪声。一会儿后，陈鑫的声音传来：</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>他感觉周遭的黑暗是粘稠的，像被极高密度的暗物质海洋吞没，每一寸空间都沉重得难以流动。这里没有星光，没有月色，好似它从未存在。黑暗在慢慢漫上来，从脚边开始，沿着脚踝，爬上膝盖，像冰冷的潮水，无声无息地漫过胸口。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒刚走一步，中弹的膝盖开始剧痛——这个剧痛让他直接跪下了。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫和叶苏明跑来搀扶漠寒，他们离裂缝越来越近，但裂缝也越来越小。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>距离裂缝还有十多步，眼看裂缝要关上，漠寒一个低头挣脱他们的搀扶，随后发力推了两人一把，两人背后带着蓝色离子，飞扑入裂缝。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>他拉开口袋，把捡来的U盘和群星丢出了空间裂缝外。瞬间，裂缝愈合。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;核心突然爆炸，一股力量推着他上升。朦胧中，他看见一个踏空而来的紫色影子，是个龙人，提着紫色长剑缓缓走近。他像是在看一个等了很久的人。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘘——</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>将军……</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;淡入&gt;&lt;中心文本&gt;裂缝外，叶苏明和云叶枫和怅然若失。叶苏明还没缓过神，大口喘气。而云叶枫站起来，拍了拍叶苏明的背。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;淡入&gt;&lt;中心文本&gt;突然，天空一声巨响，他们头顶的空间几番拉伸，一声爆炸似的声音和狂风过后，巨大的黑洞矗立在他们的头上……</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;淡入&gt;&lt;中心文本&gt;……</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;淡入&gt;&lt;中心文本&gt;正在前往漠寒线</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -3710,7 +3811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L520"/>
+  <dimension ref="A1:L549"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3" customWidth="1"/>
@@ -3767,139 +3868,136 @@
         <v>12</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>201</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="C2" s="12"/>
       <c r="D2" s="13" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>429</v>
+        <v>655</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
+      <c r="B3" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="C3" s="12"/>
       <c r="D3" s="13"/>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
       <c r="I3" s="7"/>
+      <c r="L3" s="9"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>431</v>
+        <v>390</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>633</v>
       </c>
       <c r="D4" s="13"/>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="7"/>
-      <c r="L4" s="9" t="s">
-        <v>515</v>
-      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B5" s="9" t="s">
-        <v>434</v>
+        <v>391</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>704</v>
+        <v>633</v>
       </c>
       <c r="D5" s="13"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="9" t="s">
-        <v>435</v>
+        <v>392</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>704</v>
+        <v>633</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B7" s="9" t="s">
-        <v>436</v>
+        <v>393</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>704</v>
+        <v>633</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B8" s="9" t="s">
-        <v>437</v>
+        <v>394</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>704</v>
+        <v>633</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B9" s="9" t="s">
-        <v>438</v>
+        <v>395</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>704</v>
+        <v>633</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B10" s="9" t="s">
-        <v>439</v>
+        <v>610</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>704</v>
-      </c>
-      <c r="D10" s="13"/>
+        <v>633</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B11" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>704</v>
+        <v>656</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>197</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="F11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="F12" t="s">
-        <v>18</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="D12" s="13"/>
       <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>517</v>
+        <v>468</v>
       </c>
       <c r="D13" s="13"/>
       <c r="I13" s="7"/>
@@ -3909,27 +4007,26 @@
         <v>12</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>518</v>
+        <v>473</v>
       </c>
       <c r="D14" s="13"/>
       <c r="I14" s="7"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>523</v>
+        <v>187</v>
       </c>
       <c r="D15" s="13"/>
-      <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
         <v>20</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="D16" s="13"/>
     </row>
@@ -3944,16 +4041,16 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
@@ -3962,10 +4059,10 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>469</v>
       </c>
       <c r="D20" s="13"/>
     </row>
@@ -3974,76 +4071,90 @@
         <v>19</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>519</v>
+        <v>470</v>
       </c>
       <c r="D21" s="13"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>520</v>
+        <v>474</v>
       </c>
       <c r="D22" s="13"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>524</v>
+        <v>404</v>
       </c>
       <c r="D23" s="13"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>448</v>
+        <v>471</v>
       </c>
       <c r="D24" s="13"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>521</v>
+        <v>405</v>
       </c>
       <c r="D25" s="13"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>449</v>
+        <v>186</v>
       </c>
       <c r="D26" s="13"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="D27" s="13"/>
+        <v>22</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>196</v>
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>13</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="F28" t="s">
+        <v>15</v>
+      </c>
+      <c r="L28" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
@@ -4051,44 +4162,29 @@
         <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>452</v>
+        <v>27</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F29" t="s">
-        <v>15</v>
-      </c>
-      <c r="L29" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E30" s="10" t="s">
         <v>30</v>
-      </c>
-      <c r="F30" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B31" t="s">
         <v>31</v>
@@ -4096,7 +4192,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B32" t="s">
         <v>32</v>
@@ -4104,11 +4200,23 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
         <v>33</v>
       </c>
+      <c r="D33" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
@@ -4117,1016 +4225,1005 @@
       <c r="B34" t="s">
         <v>34</v>
       </c>
-      <c r="D34" s="13" t="s">
-        <v>450</v>
+      <c r="C34" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>13</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F34" t="s">
-        <v>18</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>516</v>
+        <v>17</v>
+      </c>
+      <c r="I34" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>451</v>
+        <v>37</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F35" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="K35" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F36" t="s">
-        <v>18</v>
-      </c>
-      <c r="K36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36" t="s">
         <v>40</v>
+      </c>
+      <c r="I36" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
-      </c>
-      <c r="I37" t="s">
         <v>42</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" s="10" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
         <v>47</v>
       </c>
+      <c r="C40" s="10" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B41" t="s">
-        <v>48</v>
+      <c r="B41" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>453</v>
+        <v>410</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B44" t="s">
+      <c r="B44" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F44" t="s">
         <v>53</v>
       </c>
+      <c r="L44" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B45" t="s">
-        <v>54</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>454</v>
+      <c r="B45" s="9" t="s">
+        <v>661</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>39</v>
+        <v>52</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>455</v>
+        <v>476</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="D46" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="10" t="s">
         <v>56</v>
       </c>
       <c r="F46" t="s">
+        <v>17</v>
+      </c>
+      <c r="L46" t="s">
         <v>57</v>
-      </c>
-      <c r="L46" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B47" s="9" t="s">
-        <v>526</v>
+        <v>477</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>14</v>
+        <v>58</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="F47" t="s">
+        <v>15</v>
+      </c>
+      <c r="L47" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B48" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F48" t="s">
-        <v>18</v>
-      </c>
-      <c r="L48" t="s">
-        <v>61</v>
+        <v>478</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B49" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>699</v>
-      </c>
-      <c r="F49" t="s">
-        <v>15</v>
-      </c>
-      <c r="L49" t="s">
-        <v>63</v>
+        <v>479</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B50" s="9" t="s">
-        <v>529</v>
+        <v>480</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B51" s="9" t="s">
-        <v>530</v>
+        <v>481</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B52" s="9" t="s">
-        <v>531</v>
+        <v>482</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B53" s="9" t="s">
-        <v>532</v>
+      <c r="A53" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" t="s">
+        <v>61</v>
+      </c>
+      <c r="L53" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A54" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="B54" s="9" t="s">
-        <v>533</v>
+        <v>662</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B55" t="s">
-        <v>65</v>
-      </c>
-      <c r="L55" t="s">
-        <v>64</v>
+      <c r="A55" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>663</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>698</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="L56" s="9" t="s">
-        <v>208</v>
+        <v>664</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A57" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="I57" t="s">
-        <v>66</v>
-      </c>
-      <c r="K57" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="L57" t="s">
-        <v>64</v>
+      <c r="A57" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="L57" s="9" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A58" s="3" t="s">
-        <v>67</v>
+      <c r="A58" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="I58" t="s">
+        <v>62</v>
+      </c>
+      <c r="K58" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="L58" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B59" t="s">
-        <v>68</v>
-      </c>
-      <c r="I59" t="s">
-        <v>69</v>
-      </c>
-      <c r="L59" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A60" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>64</v>
+      </c>
+      <c r="I60" t="s">
+        <v>65</v>
+      </c>
+      <c r="L60" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>73</v>
-      </c>
-      <c r="L62" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A63" s="3" t="s">
-        <v>67</v>
+      <c r="B63" t="s">
+        <v>69</v>
+      </c>
+      <c r="L63" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B64" t="s">
-        <v>75</v>
-      </c>
-      <c r="I64" t="s">
-        <v>76</v>
-      </c>
-      <c r="L64" t="s">
-        <v>77</v>
+      <c r="B64" s="9" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B65" t="s">
-        <v>78</v>
-      </c>
-      <c r="L65" t="s">
-        <v>74</v>
+      <c r="A65" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A66" s="3" t="s">
-        <v>67</v>
+      <c r="A66" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A67" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B67" t="s">
-        <v>79</v>
-      </c>
-      <c r="I67" t="s">
-        <v>80</v>
-      </c>
-      <c r="L67" t="s">
-        <v>81</v>
+      <c r="A67" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>668</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B68" t="s">
-        <v>82</v>
-      </c>
+      <c r="A68" s="11"/>
+      <c r="B68" s="9"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B69" t="s">
-        <v>83</v>
-      </c>
-      <c r="L69" t="s">
-        <v>74</v>
+      <c r="A69" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>67</v>
+        <v>12</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="I70" t="s">
+        <v>71</v>
+      </c>
+      <c r="L70" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A71" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B71" t="s">
-        <v>84</v>
-      </c>
-      <c r="I71" t="s">
-        <v>85</v>
+      <c r="B71" s="9" t="s">
+        <v>670</v>
       </c>
       <c r="L71" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B72" t="s">
-        <v>87</v>
+      <c r="A72" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A73" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="B73" t="s">
-        <v>88</v>
+        <v>73</v>
+      </c>
+      <c r="I73" t="s">
+        <v>74</v>
+      </c>
+      <c r="L73" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
-        <v>89</v>
-      </c>
-      <c r="L74" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A75" s="3" t="s">
-        <v>67</v>
+      <c r="B75" t="s">
+        <v>77</v>
+      </c>
+      <c r="L75" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B76" t="s">
-        <v>90</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="I76" t="s">
-        <v>92</v>
-      </c>
-      <c r="L76" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>94</v>
+        <v>78</v>
+      </c>
+      <c r="I77" t="s">
+        <v>79</v>
+      </c>
+      <c r="L77" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A78" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B78" t="s">
-        <v>95</v>
-      </c>
-      <c r="L78" t="s">
-        <v>74</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B79" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B80" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="I80" t="s">
-        <v>96</v>
+      <c r="B80" t="s">
+        <v>83</v>
+      </c>
+      <c r="L80" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B82" s="9" t="s">
-        <v>212</v>
+      <c r="B82" t="s">
+        <v>84</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>85</v>
       </c>
       <c r="I82" t="s">
-        <v>97</v>
+        <v>86</v>
+      </c>
+      <c r="L82" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B83" s="9" t="s">
-        <v>440</v>
+      <c r="A83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B83" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B84" s="9" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B85" s="9" t="s">
-        <v>442</v>
+      <c r="A84" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B84" t="s">
+        <v>89</v>
+      </c>
+      <c r="L84" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A86" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B86" s="9" t="s">
-        <v>213</v>
+        <v>412</v>
+      </c>
+      <c r="I86" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B87" s="9" t="s">
-        <v>534</v>
+        <v>63</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B88" t="s">
-        <v>98</v>
+      <c r="B88" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="I88" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A89" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B89" t="s">
-        <v>99</v>
-      </c>
-      <c r="C89" s="10" t="s">
-        <v>44</v>
+      <c r="B89" s="9" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A90" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B90" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="C90" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D90" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="L90" t="s">
-        <v>63</v>
+        <v>397</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B91" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="D91" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="F91" t="s">
-        <v>18</v>
-      </c>
-      <c r="L91" t="s">
-        <v>101</v>
+        <v>398</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A92" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B92" s="9" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>217</v>
+        <v>483</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>218</v>
+        <v>45</v>
+      </c>
+      <c r="B95" t="s">
+        <v>93</v>
+      </c>
+      <c r="C95" s="10" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>219</v>
+        <v>191</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="L96" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A97" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B97" s="9" t="s">
-        <v>220</v>
+        <v>190</v>
+      </c>
+      <c r="D97" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F97" t="s">
+        <v>17</v>
+      </c>
+      <c r="L97" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A98" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B98" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="C98" s="10" t="s">
-        <v>103</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B100" t="s">
-        <v>104</v>
+        <v>22</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B101" s="9" t="s">
-        <v>225</v>
+      <c r="B101" s="4" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="L102" t="s">
-        <v>106</v>
+        <v>195</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B103" t="s">
-        <v>107</v>
+        <v>12</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B104" t="s">
-        <v>108</v>
+      <c r="B104" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B106" s="9" t="s">
-        <v>227</v>
+        <v>12</v>
+      </c>
+      <c r="B106" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>228</v>
+        <v>12</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>230</v>
+        <v>98</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="L108" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B109" s="4" t="s">
-        <v>231</v>
+      <c r="A109" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B109" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B110" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="C110" s="10" t="s">
+      <c r="B110" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A111" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A112" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="B119" t="s">
+        <v>102</v>
+      </c>
+      <c r="C119" s="10" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A111" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A112" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A113" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="E113" s="10" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A114" s="11" t="s">
-        <v>544</v>
-      </c>
-      <c r="B114" t="s">
-        <v>109</v>
-      </c>
-      <c r="C114" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E114" s="10" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A115" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="C115" s="12" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A116" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="C116" s="12"/>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A117" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="C117" s="12"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A118" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>537</v>
-      </c>
-      <c r="C118" s="12"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A119" s="11" t="s">
-        <v>545</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="C119" s="12"/>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A120" s="11" t="s">
-        <v>544</v>
+      <c r="E119" s="10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="C120" s="12"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+        <v>209</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="11" t="s">
-        <v>545</v>
+        <v>206</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
       <c r="C121" s="12"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>541</v>
+        <v>485</v>
       </c>
       <c r="C122" s="12"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>542</v>
+        <v>486</v>
       </c>
       <c r="C123" s="12"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A124" s="3" t="s">
-        <v>12</v>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" s="11" t="s">
+        <v>494</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>543</v>
+        <v>487</v>
       </c>
       <c r="C124" s="12"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" s="11" t="s">
+        <v>493</v>
+      </c>
       <c r="B125" s="4" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+        <v>488</v>
+      </c>
+      <c r="C125" s="12"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126" s="11" t="s">
+        <v>494</v>
+      </c>
       <c r="B126" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="C126" s="12" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+        <v>489</v>
+      </c>
+      <c r="C126" s="12"/>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="C127" s="11" t="s">
-        <v>458</v>
-      </c>
-      <c r="F127" s="9" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A128" s="11" t="s">
-        <v>240</v>
+        <v>490</v>
+      </c>
+      <c r="C127" s="12"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="C128" s="12" t="s">
-        <v>459</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="C128" s="12"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>546</v>
-      </c>
-      <c r="C129" s="12" t="s">
-        <v>460</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="C129" s="12"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A130" s="11" t="s">
-        <v>240</v>
-      </c>
       <c r="B130" s="4" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A131" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B131" s="4" t="s">
-        <v>461</v>
+        <v>211</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>462</v>
-      </c>
-      <c r="D131" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="G131" s="9" t="s">
-        <v>272</v>
+        <v>413</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B132" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="C132" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="D132" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="F132" t="s">
-        <v>18</v>
-      </c>
-      <c r="G132" s="9" t="s">
-        <v>463</v>
+        <v>212</v>
+      </c>
+      <c r="C132" s="11" t="s">
+        <v>414</v>
+      </c>
+      <c r="F132" s="9" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="11" t="s">
+        <v>214</v>
+      </c>
       <c r="B133" s="4" t="s">
-        <v>547</v>
+        <v>213</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="G133" s="9" t="s">
-        <v>272</v>
+        <v>415</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B134" s="4" t="s">
-        <v>247</v>
+        <v>495</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A135" s="3" t="s">
-        <v>12</v>
+      <c r="A135" s="11" t="s">
+        <v>214</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>244</v>
+        <v>215</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>248</v>
+        <v>417</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="D136" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="G136" s="9" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A137" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B137" s="4" t="s">
-        <v>249</v>
+        <v>216</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D137" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="F137" t="s">
+        <v>17</v>
+      </c>
+      <c r="G137" s="9" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A138" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="B138" s="4" t="s">
-        <v>250</v>
+        <v>496</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="G138" s="9" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A139" s="11" t="s">
-        <v>252</v>
-      </c>
       <c r="B139" s="4" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C140" s="12" t="s">
-        <v>254</v>
+        <v>218</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="C141" s="12"/>
+        <v>222</v>
+      </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A144" s="3" t="s">
-        <v>12</v>
+      <c r="A144" s="11" t="s">
+        <v>226</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
@@ -5134,7 +5231,10 @@
         <v>19</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>258</v>
+        <v>227</v>
+      </c>
+      <c r="C145" s="12" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
@@ -5142,318 +5242,313 @@
         <v>12</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="C146" s="12" t="s">
-        <v>259</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="C146" s="12"/>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A147" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="B147" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="D147" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="E147" s="12" t="s">
-        <v>465</v>
+        <v>229</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A148" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="B148" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="C148" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="D148" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="E148" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="L148" t="s">
-        <v>58</v>
+        <v>230</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A149" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B149" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D149" s="13" t="s">
-        <v>467</v>
-      </c>
-      <c r="E149" s="12" t="s">
-        <v>700</v>
+        <v>231</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="D150" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="F150" s="9" t="s">
-        <v>390</v>
+        <v>232</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="D151" s="13" t="s">
-        <v>466</v>
-      </c>
-      <c r="F151" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="H151" s="9" t="s">
-        <v>272</v>
+        <v>211</v>
+      </c>
+      <c r="C151" s="12" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A152" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B152" s="4" t="s">
-        <v>264</v>
+        <v>234</v>
+      </c>
+      <c r="D152" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="E152" s="12" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A153" s="11" t="s">
-        <v>232</v>
-      </c>
       <c r="B153" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="H153" s="9" t="s">
-        <v>272</v>
+        <v>211</v>
+      </c>
+      <c r="C153" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="D153" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="E153" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="L153" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A154" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B154" s="4" t="s">
-        <v>265</v>
+        <v>236</v>
+      </c>
+      <c r="D154" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="E154" s="12" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A155" s="11" t="s">
-        <v>275</v>
+      <c r="A155" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>274</v>
+        <v>497</v>
       </c>
       <c r="D155" s="13" t="s">
-        <v>466</v>
-      </c>
-      <c r="E155" s="12"/>
-      <c r="H155" s="9" t="s">
-        <v>272</v>
+        <v>174</v>
+      </c>
+      <c r="F155" s="9" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A156" s="11" t="s">
-        <v>276</v>
+      <c r="A156" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>277</v>
+        <v>237</v>
       </c>
       <c r="D156" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="E156" s="12"/>
+        <v>422</v>
+      </c>
       <c r="F156" s="9" t="s">
-        <v>390</v>
+        <v>351</v>
       </c>
       <c r="H156" s="9" t="s">
-        <v>272</v>
+        <v>245</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C157" s="12" t="s">
-        <v>468</v>
-      </c>
-      <c r="D157" s="13" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A158" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="H158" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="E157" s="12"/>
-      <c r="F157" s="9" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A158" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>268</v>
-      </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A159" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B159" s="4" t="s">
-        <v>269</v>
+        <v>239</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A160" s="11" t="s">
+        <v>248</v>
+      </c>
       <c r="B160" s="4" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
+        <v>247</v>
+      </c>
+      <c r="D160" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="E160" s="12"/>
+      <c r="H160" s="9" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A161" s="11" t="s">
+        <v>249</v>
+      </c>
       <c r="B161" s="4" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
+        <v>250</v>
+      </c>
+      <c r="D161" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="E161" s="12"/>
+      <c r="F161" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="H161" s="9" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A162" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="B162" s="4" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
+        <v>241</v>
+      </c>
+      <c r="C162" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="D162" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="E162" s="12"/>
+      <c r="F162" s="9" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A164" s="3" t="s">
-        <v>19</v>
-      </c>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B164" s="4" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A165" s="11" t="s">
-        <v>240</v>
-      </c>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B165" s="4" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A166" s="3" t="s">
-        <v>12</v>
-      </c>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B166" s="4" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A167" s="11" t="s">
-        <v>222</v>
-      </c>
+        <v>631</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B167" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A169" s="11" t="s">
-        <v>240</v>
+        <v>672</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A169" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A170" s="3" t="s">
-        <v>12</v>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A170" s="11" t="s">
+        <v>214</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A171" s="11" t="s">
-        <v>240</v>
+        <v>673</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A171" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="C171" s="12" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="11" t="s">
-        <v>292</v>
+        <v>198</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="C172" s="12" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="C173" s="12" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A174" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="B174" s="4" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A174" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B174" s="4" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A175" s="11" t="s">
-        <v>240</v>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A175" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A176" s="3" t="s">
-        <v>12</v>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A176" s="11" t="s">
+        <v>214</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>451</v>
+        <v>633</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" s="11" t="s">
-        <v>222</v>
+        <v>259</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>291</v>
+        <v>257</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
@@ -5461,31 +5556,35 @@
         <v>12</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>293</v>
+        <v>675</v>
+      </c>
+      <c r="C178" s="12" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179" s="11" t="s">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>294</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="C179" s="12"/>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A180" s="11" t="s">
-        <v>222</v>
+      <c r="A180" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>295</v>
+        <v>676</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A181" s="11" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>296</v>
+        <v>677</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
@@ -5493,49 +5592,58 @@
         <v>12</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>297</v>
+        <v>678</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183" s="11" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>298</v>
+        <v>679</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A184" s="3" t="s">
-        <v>12</v>
+      <c r="A184" s="11" t="s">
+        <v>214</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>300</v>
+        <v>680</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A185" s="11" t="s">
-        <v>232</v>
+      <c r="A185" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>299</v>
+        <v>681</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A186" s="3" t="s">
-        <v>12</v>
+      <c r="A186" s="11" t="s">
+        <v>214</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>549</v>
+        <v>682</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A187" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B187" s="4" t="s">
-        <v>469</v>
+        <v>683</v>
+      </c>
+      <c r="C187" s="12" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A188" s="11" t="s">
+        <v>198</v>
+      </c>
       <c r="B188" s="4" t="s">
-        <v>301</v>
+        <v>258</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
@@ -5543,645 +5651,619 @@
         <v>12</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="C189" s="12" t="s">
-        <v>704</v>
+        <v>260</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A190" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A191" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A192" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A193" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A194" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A195" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A196" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A197" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B198" s="4" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B199" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A200" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C200" s="12" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A201" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C201" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A202" s="11"/>
+      <c r="B202" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C202" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A203" s="11"/>
+      <c r="B203" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C203" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A204" s="11"/>
+      <c r="B204" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C204" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A205" s="11"/>
+      <c r="B205" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="C205" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A206" s="11"/>
+      <c r="B206" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="C206" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A207" s="11"/>
+      <c r="B207" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C207" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A208" s="11"/>
+      <c r="B208" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="C208" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A209" s="11"/>
+      <c r="B209" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C209" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A210" s="11"/>
+      <c r="B210" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C210" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A211" s="11"/>
+      <c r="B211" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C211" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A212" s="11"/>
+      <c r="B212" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C212" s="12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A213" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C213" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A214" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A215" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A216" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A217" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A218" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A219" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A220" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A221" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A222" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B222" s="8" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A223" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B223" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A224" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B224" s="8" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A225" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C225" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A226" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A227" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A228" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A229" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D229" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="E229" s="12" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A230" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D230" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E230" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="F230" t="s">
+        <v>15</v>
+      </c>
+      <c r="L230" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B231" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="E231" s="12" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B232" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="E232" s="12"/>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B233" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E233" s="12"/>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B234" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="E234" s="12"/>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B235" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="E235" s="12"/>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A236" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C236" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D236" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A237" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D237" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="F237" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A238" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A239" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="D239" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A240" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A241" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A242" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A243" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B244" s="4" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A245" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C245" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D245" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F245" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A246" s="11"/>
+      <c r="B246" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A247" s="11"/>
+      <c r="B247" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A248" s="11"/>
+      <c r="B248" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A249" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C249" s="12" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A250" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B250" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="B190" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C190" s="11" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A191" s="11"/>
-      <c r="B191" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="C191" s="11" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A192" s="11"/>
-      <c r="B192" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="C192" s="11" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A193" s="11"/>
-      <c r="B193" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="C193" s="11" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A194" s="11"/>
-      <c r="B194" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="C194" s="11" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A195" s="11"/>
-      <c r="B195" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="C195" s="11" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A196" s="11"/>
-      <c r="B196" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="C196" s="11" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A197" s="11"/>
-      <c r="B197" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="C197" s="11" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A198" s="11"/>
-      <c r="B198" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="C198" s="11" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A199" s="11"/>
-      <c r="B199" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="C199" s="11" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A200" s="11"/>
-      <c r="B200" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="C200" s="11" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A201" s="11"/>
-      <c r="B201" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="C201" s="12" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A202" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="B202" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="C202" s="11" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A203" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B203" s="4" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A204" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B204" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A205" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B205" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A206" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B206" s="4" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A207" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B207" s="4" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A208" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B208" s="4" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A209" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B209" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A210" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B210" s="8" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A211" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B211" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A212" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B212" s="8" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A213" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B213" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="C213" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A214" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B214" s="4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A215" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B215" s="4" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A216" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B216" s="4" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A217" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B217" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="D217" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="E217" s="12" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A218" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B218" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="D218" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E218" s="12" t="s">
-        <v>701</v>
-      </c>
-      <c r="F218" t="s">
-        <v>15</v>
-      </c>
-      <c r="L218" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B219" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E219" s="12" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A220" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B220" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C220" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D220" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A221" s="3" t="s">
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A251" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A252" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A253" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B221" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="D221" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="F221" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A222" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B222" s="4" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A223" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B223" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="D223" s="14" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A224" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="B224" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="C224" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D224" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="F224" t="s">
+      <c r="B253" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A254" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A255" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A256" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D256" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E256" s="10" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A257" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="D257" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="E257" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="F257" s="9" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A258" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A225" s="11"/>
-      <c r="B225" s="4" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A226" s="11"/>
-      <c r="B226" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A227" s="11"/>
-      <c r="B227" s="4" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A228" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="B228" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="C228" s="12" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A229" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B229" s="4" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A230" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B230" s="4" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A231" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B231" s="4" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A232" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B232" s="4" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A233" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B233" s="4" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A234" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B234" s="4" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A235" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B235" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="D235" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="E235" s="10" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A236" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B236" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="D236" s="13" t="s">
-        <v>433</v>
-      </c>
-      <c r="E236" s="10" t="s">
-        <v>695</v>
-      </c>
-      <c r="F236" s="9" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A237" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B237" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A238" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B238" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A239" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="B239" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="C239" s="12" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A240" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="B240" s="4" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A241" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B241" s="4" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A242" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B242" s="9" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A243" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B243" s="4" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A244" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B244" s="4" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A245" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B245" s="4" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A246" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B246" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="L246" s="9" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B247" s="4" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B248" s="4" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A249" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B249" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A250" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B250" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G250" s="9" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B251" s="4" t="s">
-        <v>692</v>
-      </c>
-      <c r="G251" t="s">
-        <v>129</v>
-      </c>
-      <c r="L251" s="9" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B252" s="4" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A253" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B253" s="4" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A254" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="B254" s="4" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A255" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B255" s="4" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A256" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B256" s="4" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A257" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="B257" s="4" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A258" s="11" t="s">
-        <v>200</v>
-      </c>
       <c r="B258" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="C258" s="12" t="s">
-        <v>481</v>
-      </c>
-      <c r="L258" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.2">
@@ -6189,73 +6271,58 @@
         <v>12</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>353</v>
+        <v>115</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A260" s="11" t="s">
+        <v>302</v>
+      </c>
       <c r="B260" s="4" t="s">
-        <v>482</v>
+        <v>300</v>
       </c>
       <c r="C260" s="12" t="s">
-        <v>243</v>
+        <v>429</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A261" s="11" t="s">
+        <v>312</v>
+      </c>
       <c r="B261" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="C261" s="12" t="s">
-        <v>484</v>
-      </c>
-      <c r="L261" t="s">
-        <v>58</v>
+        <v>303</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A262" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B262" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="C262" s="12" t="s">
-        <v>481</v>
+        <v>304</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A263" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B263" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="C263" s="12" t="s">
-        <v>243</v>
+        <v>19</v>
+      </c>
+      <c r="B263" s="9" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A264" s="11" t="s">
-        <v>352</v>
+      <c r="A264" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C264" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="G264" t="s">
-        <v>129</v>
+        <v>306</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A265" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>689</v>
-      </c>
-      <c r="C265" s="12" t="s">
-        <v>485</v>
-      </c>
-      <c r="G265" t="s">
-        <v>130</v>
+        <v>307</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.2">
@@ -6263,50 +6330,36 @@
         <v>12</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="C266" s="12" t="s">
-        <v>417</v>
+        <v>308</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A267" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="B267" s="4"/>
-      <c r="C267" s="12" t="s">
-        <v>455</v>
+      <c r="A267" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="L267" s="9" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A268" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B268" s="4" t="s">
-        <v>706</v>
-      </c>
-      <c r="C268" s="12"/>
+        <v>431</v>
+      </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A269" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B269" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="C269" s="12" t="s">
-        <v>459</v>
+        <v>432</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A270" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="G270" t="s">
-        <v>60</v>
+        <v>433</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.2">
@@ -6314,1236 +6367,1194 @@
         <v>12</v>
       </c>
       <c r="B271" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="G271" s="9" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B272" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="G272" t="s">
+        <v>119</v>
+      </c>
+      <c r="L272" s="9" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="273" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B273" s="4" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A274" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="275" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A275" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="276" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A276" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="277" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A277" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="278" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A278" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="279" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A279" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B279" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C279" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="L279" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="280" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A280" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B280" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="281" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B281" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="C281" s="12" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="282" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B282" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C282" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="L282" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="283" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B283" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C283" s="12" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="284" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A284" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B284" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="C284" s="12" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="285" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A285" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="B285" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C285" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="G285" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="286" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A286" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B286" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="C286" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="G286" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="287" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A287" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C287" s="12" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="288" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A288" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B288" s="4"/>
+      <c r="C288" s="12" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A289" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="C289" s="12"/>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A290" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="C290" s="12" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A291" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B291" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="G291" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A292" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B292" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A293" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B293" s="4" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A294" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B294" s="4" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A295" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B295" s="4" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A296" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B296" s="4" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A297" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B297" s="4" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A298" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B298" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="C298" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A299" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A300" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B300" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A301" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B301" s="4" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B302" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="C302" s="10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B303" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="D303" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="E303" s="10" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A304" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B304" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="C304" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D304" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="E304" s="10" t="s">
+        <v>625</v>
+      </c>
+      <c r="F304" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A305" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B305" s="4" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A306" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B306" s="4" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A307" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B307" s="4" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B308" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="C308" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D308" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E308" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="F308" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B309" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A310" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B310" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A311" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B311" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A312" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B312" s="4"/>
+      <c r="K312" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A313" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B313" s="4" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A272" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B272" s="4" t="s">
+      <c r="D313" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E313" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="I313" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A273" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B273" s="4" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A274" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B274" s="4" t="s">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A314" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="B314" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="C314" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D314" s="14" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A275" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B275" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="C275" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A276" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B276" s="4" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A277" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B277" s="4" t="s">
+      <c r="E314" s="12" t="s">
+        <v>637</v>
+      </c>
+      <c r="F314" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A315" s="11"/>
+      <c r="B315" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="C315" s="3"/>
+    </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A316" s="11"/>
+      <c r="B316" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="C316" s="3"/>
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A317" s="11"/>
+      <c r="B317" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="C317" s="3"/>
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A318" s="11"/>
+      <c r="B318" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="C318" s="3"/>
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A319" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C319" s="3"/>
+      <c r="D319" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="E319" s="12" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A320" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B320" s="4" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A278" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B278" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B279" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C279" s="10" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B280" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="D280" s="13" t="s">
-        <v>433</v>
-      </c>
-      <c r="E280" s="10" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B281" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C281" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="D281" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="E281" s="10" t="s">
-        <v>696</v>
-      </c>
-      <c r="F281" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B282" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C282" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D282" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="E282" s="10" t="s">
-        <v>694</v>
-      </c>
-      <c r="F282" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B283" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A284" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B284" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A285" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B285" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A286" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B286" s="4"/>
-      <c r="K286" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A287" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B287" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="D287" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="E287" s="10" t="s">
-        <v>694</v>
-      </c>
-      <c r="I287" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A288" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="B288" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="C288" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D288" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="E288" s="12" t="s">
-        <v>708</v>
-      </c>
-      <c r="F288" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A289" s="11"/>
-      <c r="B289" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C289" s="3"/>
-    </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A290" s="11"/>
-      <c r="B290" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="C290" s="3"/>
-    </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A291" s="11"/>
-      <c r="B291" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C291" s="3"/>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A292" s="11"/>
-      <c r="B292" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="C292" s="3"/>
-    </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A293" s="11"/>
-      <c r="B293" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C293" s="3"/>
-    </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A294" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="B294" s="4" t="s">
-        <v>550</v>
-      </c>
-      <c r="C294" s="3"/>
-      <c r="D294" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="E294" s="12" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A295" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B295" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D295" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="E295" s="10" t="s">
-        <v>694</v>
-      </c>
-      <c r="F295" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B296" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C296" s="10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B297" s="4" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B298" s="4" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A299" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B299" s="4" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A300" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B300" s="4" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A301" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="B301" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="D301" s="13" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A302" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B302" s="4" t="s">
-        <v>557</v>
-      </c>
-      <c r="E302" s="12" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B303" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="C303" s="12" t="s">
-        <v>562</v>
-      </c>
-      <c r="D303" s="13" t="s">
-        <v>433</v>
-      </c>
-      <c r="E303" s="12" t="s">
-        <v>695</v>
-      </c>
-      <c r="F303" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A304" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B304" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="C304" s="12" t="s">
-        <v>563</v>
-      </c>
-      <c r="D304" s="13" t="s">
-        <v>433</v>
-      </c>
-      <c r="E304" s="12" t="s">
-        <v>695</v>
-      </c>
-      <c r="I304" s="9"/>
-    </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A305" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B305" s="4" t="s">
-        <v>565</v>
-      </c>
-      <c r="C305" s="12"/>
-      <c r="D305" s="13"/>
-      <c r="E305" s="12"/>
-      <c r="I305" s="9"/>
-    </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A306" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="B306" s="4"/>
-      <c r="C306" s="12" t="s">
-        <v>564</v>
-      </c>
-      <c r="D306" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="E306" s="12" t="s">
-        <v>707</v>
-      </c>
-      <c r="F306" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A307" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B307" s="4" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A308" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="B308" s="4" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A309" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B309" s="4" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A310" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B310" s="4" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A311" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B311" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C311" s="10" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A312" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B312" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A313" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B313" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="L313" s="9" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A314" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="B314" s="4"/>
-      <c r="C314" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="L314" s="9" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A315" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B315" s="4" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A316" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B316" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A317" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B317" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A318" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B318" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E318" s="10" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A319" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B319" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="C319" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D319" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="E319" s="10" t="s">
-        <v>695</v>
-      </c>
-      <c r="L319" s="9" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A320" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B320" s="4" t="s">
-        <v>362</v>
-      </c>
       <c r="D320" s="14" t="s">
-        <v>164</v>
+        <v>126</v>
+      </c>
+      <c r="E320" s="10" t="s">
+        <v>623</v>
       </c>
       <c r="F320" t="s">
         <v>15</v>
       </c>
-      <c r="L320" s="9" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A321" s="3" t="s">
-        <v>20</v>
-      </c>
+    </row>
+    <row r="321" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B321" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A322" s="3" t="s">
-        <v>46</v>
-      </c>
+        <v>723</v>
+      </c>
+      <c r="C321" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="322" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B322" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C322" s="10" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A323" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>499</v>
+      </c>
+    </row>
+    <row r="323" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B323" s="4" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A324" s="3" t="s">
-        <v>12</v>
-      </c>
+        <v>724</v>
+      </c>
+    </row>
+    <row r="324" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B324" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A325" s="3" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="325" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B325" s="4" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="326" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B326" s="4" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="327" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B327" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="D327" s="13" t="s">
+        <v>500</v>
+      </c>
+      <c r="E327" s="12" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="328" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A328" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B328" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="D328" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="E328" s="12" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="329" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A329" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B329" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="D329" s="13"/>
+      <c r="E329" s="12"/>
+    </row>
+    <row r="330" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A330" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B330" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="C330" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="I330" s="9"/>
+    </row>
+    <row r="331" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A331" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B331" s="4"/>
+      <c r="C331" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="D331" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E331" s="12" t="s">
+        <v>636</v>
+      </c>
+      <c r="F331" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="332" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A332" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B332" s="4" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="333" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A333" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B333" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="C333" s="10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="334" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A334" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B334" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="335" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A335" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B335" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="L335" s="9" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="336" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A336" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B336" s="4"/>
+      <c r="C336" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B325" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C325" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B326" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C326" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A327" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B327" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="C327" s="10" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A328" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B328" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="C328" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B329" s="4" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A330" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B330" s="4" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A331" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B331" s="4" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A332" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B332" s="4" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A333" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B333" s="4" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A334" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B334" s="4" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A335" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="B335" s="4" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A336" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B336" s="4" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="L336" s="9" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="337" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A337" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="D337" s="14" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="338" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A338" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="D338" s="13" t="s">
-        <v>675</v>
-      </c>
-      <c r="F338" s="9" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="339" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A339" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="340" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A340" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+      <c r="E340" s="10" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="341" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A341" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="D341" s="13" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A342" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="B342" s="4"/>
-      <c r="D342" s="13" t="s">
-        <v>676</v>
-      </c>
-      <c r="F342" s="9" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
+        <v>506</v>
+      </c>
+      <c r="C341" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D341" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E341" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="L341" s="9" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="342" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A342" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B342" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D342" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="F342" t="s">
+        <v>15</v>
+      </c>
+      <c r="L342" s="9" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="343" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A343" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>683</v>
-      </c>
-      <c r="D343" s="13"/>
-      <c r="F343" s="9"/>
-    </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="344" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A344" s="3" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="D344" s="13" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A345" s="11" t="s">
-        <v>222</v>
+        <v>146</v>
+      </c>
+      <c r="C344" s="10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="345" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A345" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="D345" s="13" t="s">
-        <v>675</v>
-      </c>
-      <c r="F345" s="9" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="346" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A346" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A347" s="11" t="s">
-        <v>222</v>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="347" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A347" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A348" s="3" t="s">
-        <v>12</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="C347" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="348" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B348" s="4" t="s">
-        <v>590</v>
-      </c>
-      <c r="C348" s="12" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A349" s="11" t="s">
-        <v>222</v>
+        <v>117</v>
+      </c>
+      <c r="C348" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="349" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A349" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+      <c r="C349" s="10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="350" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A350" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A351" s="11" t="s">
-        <v>232</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="C350" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="351" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B351" s="4" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A352" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
+      </c>
+    </row>
+    <row r="352" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A352" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A353" s="11" t="s">
-        <v>347</v>
+        <v>328</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A353" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A354" s="11" t="s">
-        <v>222</v>
+        <v>329</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A354" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A355" s="3" t="s">
-        <v>12</v>
+        <v>508</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A355" s="11" t="s">
+        <v>198</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.2">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A356" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.2">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A357" s="11" t="s">
-        <v>222</v>
+        <v>312</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.2">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A358" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A359" s="11" t="s">
-        <v>222</v>
+        <v>512</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A359" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A360" s="11" t="s">
-        <v>222</v>
+        <v>513</v>
+      </c>
+      <c r="D359" s="14" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A360" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.2">
+        <v>514</v>
+      </c>
+      <c r="D360" s="13" t="s">
+        <v>604</v>
+      </c>
+      <c r="F360" s="9" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A361" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.2">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A362" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="B362" s="4" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.2">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A363" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.2">
+        <v>517</v>
+      </c>
+      <c r="D363" s="13" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A364" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B364" s="4" t="s">
-        <v>603</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="B364" s="4"/>
       <c r="D364" s="13" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.2">
+        <v>605</v>
+      </c>
+      <c r="F364" s="9" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A365" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="D365" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="F365" s="9" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.2">
+        <v>612</v>
+      </c>
+      <c r="D365" s="13"/>
+      <c r="F365" s="9"/>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A366" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B366" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="D366" s="13" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A367" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B367" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="D367" s="13" t="s">
         <v>604</v>
       </c>
-      <c r="D366" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="F366" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B367" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="L367" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F367" s="9" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A368" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="B368" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L368" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.2">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A369" s="11" t="s">
+        <v>198</v>
+      </c>
       <c r="B369" s="4" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.2">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A370" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B370" s="4" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.2">
+        <v>522</v>
+      </c>
+      <c r="C370" s="12" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A371" s="11" t="s">
+        <v>198</v>
+      </c>
       <c r="B371" s="4" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.2">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A372" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B372" s="4" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.2">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A373" s="11" t="s">
+        <v>206</v>
+      </c>
       <c r="B373" s="4" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A374" s="3" t="s">
-        <v>12</v>
+        <v>526</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A374" s="11" t="s">
+        <v>288</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="L374" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.2">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A375" s="11" t="s">
-        <v>222</v>
+        <v>312</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="L375" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A376" s="3" t="s">
-        <v>12</v>
+        <v>528</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A376" s="11" t="s">
+        <v>198</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="E376" s="12" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A377" s="11" t="s">
-        <v>222</v>
+        <v>529</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A377" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="E377" s="12" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.2">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A378" s="3" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="E378" s="10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A379" s="3" t="s">
-        <v>12</v>
+        <v>614</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A379" s="11" t="s">
+        <v>198</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.2">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A380" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B380" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="L380" s="9" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A381" s="11" t="s">
+        <v>198</v>
+      </c>
       <c r="B381" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="D381" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="E381" s="10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.2">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A382" s="11" t="s">
+        <v>198</v>
+      </c>
       <c r="B382" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="C382" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="D382" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="E382" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="L382" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.2">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A383" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B383" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="D383" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="E383" s="12" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.2">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B384" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="D384" s="13" t="s">
-        <v>494</v>
-      </c>
-      <c r="E384" s="12"/>
-      <c r="F384" s="9" t="s">
-        <v>390</v>
+        <v>533</v>
       </c>
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A385" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B385" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="L385" s="9"/>
+        <v>534</v>
+      </c>
     </row>
     <row r="386" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A386" s="3" t="s">
-        <v>12</v>
+      <c r="A386" s="11" t="s">
+        <v>206</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>693</v>
+        <v>535</v>
       </c>
       <c r="D386" s="13" t="s">
-        <v>494</v>
-      </c>
-      <c r="I386" s="9" t="s">
-        <v>716</v>
-      </c>
-      <c r="L386" s="9" t="s">
-        <v>687</v>
+        <v>604</v>
       </c>
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A387" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="B387" s="4"/>
-      <c r="C387" s="12" t="s">
-        <v>499</v>
-      </c>
-      <c r="D387" s="12" t="s">
-        <v>713</v>
-      </c>
-      <c r="L387" s="9" t="s">
-        <v>714</v>
+      <c r="A387" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B387" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="D387" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="F387" s="9" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="388" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A388" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B388" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="C388" s="12" t="s">
-        <v>499</v>
-      </c>
-      <c r="D388" s="13" t="s">
-        <v>494</v>
-      </c>
-      <c r="I388" s="9" t="s">
-        <v>715</v>
-      </c>
-      <c r="L388" s="9" t="s">
-        <v>718</v>
+        <v>536</v>
+      </c>
+      <c r="D388" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="F388" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="389" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A389" s="11" t="s">
-        <v>232</v>
-      </c>
       <c r="B389" s="4" t="s">
-        <v>379</v>
+        <v>537</v>
+      </c>
+      <c r="L389" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="390" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A390" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B390" s="4" t="s">
-        <v>380</v>
+        <v>152</v>
+      </c>
+      <c r="L390" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="391" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B391" s="4" t="s">
-        <v>500</v>
+        <v>331</v>
       </c>
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B392" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="C392" s="12" t="s">
-        <v>505</v>
+        <v>332</v>
       </c>
     </row>
     <row r="393" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A393" s="11" t="s">
-        <v>232</v>
-      </c>
       <c r="B393" s="4" t="s">
-        <v>504</v>
+        <v>336</v>
       </c>
     </row>
     <row r="394" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A394" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B394" s="4" t="s">
-        <v>502</v>
+        <v>335</v>
       </c>
     </row>
     <row r="395" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A395" s="11" t="s">
-        <v>232</v>
-      </c>
       <c r="B395" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="D395" s="13"/>
-      <c r="I395" s="9"/>
+        <v>333</v>
+      </c>
     </row>
     <row r="396" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A396" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="C396" s="12" t="s">
-        <v>499</v>
-      </c>
-      <c r="I396" s="9"/>
-      <c r="L396" s="9"/>
+        <v>334</v>
+      </c>
+      <c r="L396" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="397" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A397" s="11" t="s">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="D397" s="13" t="s">
-        <v>494</v>
+        <v>337</v>
+      </c>
+      <c r="L397" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="398" spans="1:12" x14ac:dyDescent="0.2">
@@ -7551,797 +7562,841 @@
         <v>12</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="C398" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="D398" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="F398" s="9" t="s">
-        <v>390</v>
+        <v>442</v>
+      </c>
+      <c r="E398" s="12" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A399" s="11" t="s">
+        <v>198</v>
+      </c>
       <c r="B399" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="C399" s="12"/>
-      <c r="D399" s="13"/>
+        <v>338</v>
+      </c>
+      <c r="E399" s="12" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="400" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A400" s="3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="F400" s="9"/>
-    </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A401" s="11" t="s">
-        <v>232</v>
+        <v>658</v>
+      </c>
+      <c r="E400" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="401" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A401" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="B401" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="402" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B402" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="L402" s="9" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="403" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B403" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D403" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E403" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="404" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B404" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="C404" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D404" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="E404" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="L404" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="405" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B405" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="D405" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="E405" s="12" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="406" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B406" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="D406" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="E406" s="12"/>
+      <c r="F406" s="9" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="407" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B407" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="L407" s="9"/>
+    </row>
+    <row r="408" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A408" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B408" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D408" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="I408" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="L408" s="9" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="409" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A409" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B409" s="4"/>
+      <c r="C409" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="D409" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="L409" s="9" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="410" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A410" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B410" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="C410" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="D410" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="I410" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="L410" s="9" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="411" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A411" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B411" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="412" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A412" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B412" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="413" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B413" s="4" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="414" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B414" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="C414" s="12" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="415" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A415" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B415" s="4" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="416" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A416" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B416" s="4" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="417" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A417" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B417" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="D417" s="13"/>
+      <c r="I417" s="9"/>
+    </row>
+    <row r="418" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A418" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B418" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C418" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="I418" s="9"/>
+      <c r="L418" s="9"/>
+    </row>
+    <row r="419" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A419" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B419" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="D419" s="13" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="420" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A420" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B420" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="C420" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D420" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F420" s="9" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="421" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B421" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C421" s="12"/>
+      <c r="D421" s="13"/>
+    </row>
+    <row r="422" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A422" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B422" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="F422" s="9"/>
+    </row>
+    <row r="423" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A423" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B423" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D423" s="13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="424" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A424" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B424" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="D424" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="F424" s="9" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="425" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B425" s="4" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="426" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B426" s="4" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="427" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B427" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="D427" s="13" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="428" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B428" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="C428" s="12" t="s">
+        <v>640</v>
+      </c>
+      <c r="D428" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="E428" s="12" t="s">
+        <v>639</v>
+      </c>
+      <c r="F428" s="9" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="429" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A429" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B429" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="C429" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="D429" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="D401" s="13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A402" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B402" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="D402" s="13" t="s">
-        <v>508</v>
-      </c>
-      <c r="F402" s="9" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B403" s="4" t="s">
+      <c r="E429" s="12" t="s">
+        <v>641</v>
+      </c>
+      <c r="F429" s="9" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="430" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A430" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B430" s="4" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="431" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A431" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B431" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="432" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A432" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B432" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="D432" s="13"/>
+      <c r="E432" s="12"/>
+      <c r="F432" s="9"/>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A433" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B433" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="D433" s="13"/>
+      <c r="E433" s="12"/>
+      <c r="F433" s="9"/>
+      <c r="G433" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B434" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="G434" s="9" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B435" s="4" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A436" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B436" s="4" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A437" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B437" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C437" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="H437" s="9" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A438" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B438" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C438" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="H438" s="9" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A439" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B439" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A440" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="B440" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="C440" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="H440" s="9" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A441" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B441" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C441" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="H441" s="9" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A442" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B442" s="4" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A443" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B443" s="4" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A444" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B444" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="G444" s="9" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A445" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="B445" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G445" s="9" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B404" s="4" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B405" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="D405" s="13" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B406" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="C406" s="12" t="s">
-        <v>711</v>
-      </c>
-      <c r="D406" s="13" t="s">
-        <v>389</v>
-      </c>
-      <c r="E406" s="12" t="s">
-        <v>710</v>
-      </c>
-      <c r="F406" s="9" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A407" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B407" s="4" t="s">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A446" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B446" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C446" s="10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A447" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B447" s="4" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A448" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B448" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A449" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="B449" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A450" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B450" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A451" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B451" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A452" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B452" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="C452" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A453" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="B453" s="4" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A454" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B454" s="4" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A455" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="B455" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A456" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B456" s="4" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A457" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="B457" s="4" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A458" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B458" s="4" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A459" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="B459" s="4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A460" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B460" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A461" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B461" s="4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A462" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="B462" s="4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A463" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B463" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="G463" s="9" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A464" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B464" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="G464" s="9" t="s">
         <v>608</v>
       </c>
-      <c r="C407" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="D407" s="13" t="s">
-        <v>424</v>
-      </c>
-      <c r="E407" s="12" t="s">
-        <v>712</v>
-      </c>
-      <c r="F407" s="9" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A408" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B408" s="4" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A409" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B409" s="4" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A410" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B410" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="D410" s="13"/>
-      <c r="E410" s="12"/>
-      <c r="F410" s="9"/>
-    </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A411" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B411" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="D411" s="13"/>
-      <c r="E411" s="12"/>
-      <c r="F411" s="9"/>
-      <c r="G411" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B412" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="G412" s="9" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B413" s="4" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A414" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B414" s="4" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A415" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B415" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C415" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="H415" s="9" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A416" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B416" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="C416" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="H416" s="9" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A417" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B417" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A418" s="11" t="s">
-        <v>394</v>
-      </c>
-      <c r="B418" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="C418" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="H418" s="9" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A419" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B419" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C419" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="H419" s="9" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A420" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B420" s="4" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A421" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B421" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A422" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B422" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="G422" s="9" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A423" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="B423" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="G423" s="9" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A424" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B424" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="C424" s="10" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A425" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B425" s="4" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A426" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B426" s="4" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A427" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="B427" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A428" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B428" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A429" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B429" s="4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A430" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B430" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="C430" s="10" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A431" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="B431" s="4" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A432" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B432" s="4" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A433" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="B433" s="4" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A434" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B434" s="4" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A435" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="B435" s="4" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A436" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B436" s="4" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A437" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="B437" s="4" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A438" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B438" s="4" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A439" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B439" s="4" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A440" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="B440" s="4" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A441" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B441" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="G441" s="9" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A442" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B442" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="G442" s="9" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A443" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B443" s="4" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A444" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="B444" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="G444" s="9" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A445" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B445" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="C445" s="12" t="s">
-        <v>510</v>
-      </c>
-      <c r="G445" s="9" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A446" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B446" s="4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A447" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="B447" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="D447" s="13" t="s">
-        <v>424</v>
-      </c>
-      <c r="G447" s="9" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A448" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B448" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="C448" s="12" t="s">
-        <v>459</v>
-      </c>
-      <c r="D448" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="G448" s="9" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A449" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B449" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="C449" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="D449" s="13" t="s">
-        <v>424</v>
-      </c>
-      <c r="E449" s="12" t="s">
-        <v>712</v>
-      </c>
-      <c r="G449" s="9" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A450" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="B450" s="4" t="s">
-        <v>615</v>
-      </c>
-      <c r="D450" s="13" t="s">
-        <v>446</v>
-      </c>
-      <c r="E450" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="F450" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="G450" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="L450" s="9" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A451" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B451" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="D451" s="13"/>
-      <c r="E451" s="12"/>
-      <c r="F451" s="9"/>
-      <c r="G451" s="9"/>
-    </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B452" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="D452" s="13"/>
-      <c r="E452" s="12"/>
-      <c r="F452" s="9"/>
-      <c r="G452" s="9"/>
-    </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A453" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B453" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="D453" s="13"/>
-      <c r="E453" s="12"/>
-      <c r="F453" s="9"/>
-      <c r="G453" s="9"/>
-    </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A454" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B454" s="4" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A455" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="B455" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="L455" s="9"/>
-    </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A456" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B456" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="L456" s="9"/>
-    </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A457" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B457" s="4" t="s">
-        <v>621</v>
-      </c>
-      <c r="L457" s="9"/>
-    </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A458" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="B458" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="L458" s="9"/>
-    </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A459" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B459" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="L459" s="9"/>
-    </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A460" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B460" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="L460" s="9"/>
-    </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A461" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B461" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="L461" s="9"/>
-    </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A462" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B462" s="4" t="s">
-        <v>629</v>
-      </c>
-      <c r="L462" s="9"/>
-    </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A463" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B463" s="4" t="s">
-        <v>630</v>
-      </c>
-      <c r="L463" s="9"/>
-    </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A464" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="B464" s="4" t="s">
-        <v>667</v>
-      </c>
-      <c r="L464" s="9"/>
     </row>
     <row r="465" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A465" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="L465" s="9"/>
+        <v>372</v>
+      </c>
     </row>
     <row r="466" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A466" s="11" t="s">
+        <v>359</v>
+      </c>
       <c r="B466" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="L466" s="9" t="s">
-        <v>670</v>
+        <v>373</v>
+      </c>
+      <c r="G466" s="9" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="467" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A467" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B467" s="4" t="s">
-        <v>633</v>
-      </c>
-      <c r="L467" s="9"/>
+        <v>463</v>
+      </c>
+      <c r="C467" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="G467" s="9" t="s">
+        <v>607</v>
+      </c>
     </row>
     <row r="468" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A468" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>634</v>
-      </c>
-      <c r="L468" s="9"/>
+        <v>182</v>
+      </c>
     </row>
     <row r="469" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A469" s="11" t="s">
-        <v>232</v>
+        <v>359</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>682</v>
-      </c>
-      <c r="L469" s="9"/>
+        <v>374</v>
+      </c>
+      <c r="D469" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="G469" s="9" t="s">
+        <v>607</v>
+      </c>
     </row>
     <row r="470" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A470" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="L470" s="9"/>
+        <v>211</v>
+      </c>
+      <c r="C470" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="D470" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="G470" s="9" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="471" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A471" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>725</v>
-      </c>
-      <c r="L471" s="9"/>
+        <v>548</v>
+      </c>
+      <c r="C471" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="D471" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="E471" s="12" t="s">
+        <v>641</v>
+      </c>
+      <c r="G471" s="9" t="s">
+        <v>607</v>
+      </c>
     </row>
     <row r="472" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A472" s="3" t="s">
-        <v>12</v>
+      <c r="A472" s="11" t="s">
+        <v>359</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>636</v>
-      </c>
-      <c r="L472" s="9"/>
+        <v>547</v>
+      </c>
+      <c r="D472" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="E472" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="F472" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="G472" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="L472" s="9" t="s">
+        <v>599</v>
+      </c>
     </row>
     <row r="473" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A473" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B473" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="L473" s="9"/>
+        <v>556</v>
+      </c>
+      <c r="D473" s="13"/>
+      <c r="E473" s="12"/>
+      <c r="F473" s="9"/>
+      <c r="G473" s="9"/>
     </row>
     <row r="474" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B474" s="4" t="s">
-        <v>638</v>
-      </c>
-      <c r="L474" s="9"/>
+        <v>557</v>
+      </c>
+      <c r="D474" s="13"/>
+      <c r="E474" s="12"/>
+      <c r="F474" s="9"/>
+      <c r="G474" s="9"/>
     </row>
     <row r="475" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A475" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>639</v>
-      </c>
-      <c r="D475" s="13" t="s">
-        <v>446</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="D475" s="13"/>
+      <c r="E475" s="12"/>
+      <c r="F475" s="9"/>
+      <c r="G475" s="9"/>
     </row>
     <row r="476" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A476" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="B476" s="4"/>
-      <c r="D476" s="13" t="s">
-        <v>674</v>
-      </c>
-      <c r="F476" s="9" t="s">
-        <v>447</v>
+      <c r="A476" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B476" s="4" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="477" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A477" s="3" t="s">
-        <v>12</v>
+      <c r="A477" s="11" t="s">
+        <v>359</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>641</v>
+        <v>551</v>
       </c>
       <c r="L477" s="9"/>
     </row>
@@ -8350,31 +8405,34 @@
         <v>12</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>642</v>
+        <v>552</v>
       </c>
       <c r="L478" s="9"/>
     </row>
     <row r="479" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A479" s="11" t="s">
-        <v>399</v>
+      <c r="A479" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>643</v>
+        <v>553</v>
       </c>
       <c r="L479" s="9"/>
     </row>
     <row r="480" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A480" s="3" t="s">
-        <v>12</v>
+      <c r="A480" s="11" t="s">
+        <v>359</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>644</v>
+        <v>554</v>
       </c>
       <c r="L480" s="9"/>
     </row>
     <row r="481" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A481" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B481" s="4" t="s">
-        <v>686</v>
+        <v>555</v>
       </c>
       <c r="L481" s="9"/>
     </row>
@@ -8383,19 +8441,16 @@
         <v>12</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>645</v>
-      </c>
-      <c r="C482" s="10" t="s">
-        <v>170</v>
+        <v>560</v>
       </c>
       <c r="L482" s="9"/>
     </row>
     <row r="483" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A483" s="11" t="s">
-        <v>240</v>
+        <v>198</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>646</v>
+        <v>559</v>
       </c>
       <c r="L483" s="9"/>
     </row>
@@ -8404,46 +8459,48 @@
         <v>12</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>647</v>
+        <v>561</v>
       </c>
       <c r="L484" s="9"/>
     </row>
     <row r="485" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A485" s="11" t="s">
+        <v>206</v>
+      </c>
       <c r="B485" s="4" t="s">
-        <v>648</v>
-      </c>
-      <c r="C485" s="12" t="s">
-        <v>421</v>
+        <v>562</v>
       </c>
       <c r="L485" s="9"/>
     </row>
     <row r="486" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A486" s="11" t="s">
+        <v>359</v>
+      </c>
       <c r="B486" s="4" t="s">
-        <v>649</v>
+        <v>597</v>
       </c>
       <c r="L486" s="9"/>
     </row>
     <row r="487" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A487" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B487" s="4" t="s">
-        <v>650</v>
+        <v>563</v>
       </c>
       <c r="L487" s="9"/>
     </row>
     <row r="488" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A488" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B488" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="L488" s="9"/>
+        <v>564</v>
+      </c>
+      <c r="L488" s="9" t="s">
+        <v>600</v>
+      </c>
     </row>
     <row r="489" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A489" s="11" t="s">
-        <v>232</v>
-      </c>
       <c r="B489" s="4" t="s">
-        <v>652</v>
+        <v>565</v>
       </c>
       <c r="L489" s="9"/>
     </row>
@@ -8452,370 +8509,610 @@
         <v>12</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D490" s="13" t="s">
-        <v>674</v>
-      </c>
-      <c r="L490" s="9" t="s">
-        <v>640</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="L490" s="9"/>
     </row>
     <row r="491" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A491" s="11"/>
+      <c r="A491" s="11" t="s">
+        <v>206</v>
+      </c>
       <c r="B491" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="L491" s="9"/>
+    </row>
+    <row r="492" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A492" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B492" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="L492" s="9"/>
+    </row>
+    <row r="493" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A493" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B493" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="C491" s="12" t="s">
-        <v>459</v>
-      </c>
-      <c r="D491" s="13" t="s">
-        <v>424</v>
-      </c>
-      <c r="F491" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="G491" s="9"/>
-      <c r="L491" s="9" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="492" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A492" s="11"/>
-      <c r="B492" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="G492" s="9"/>
-    </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A493" s="11"/>
-      <c r="B493" s="4" t="s">
-        <v>655</v>
-      </c>
-      <c r="C493" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="G493" s="9"/>
       <c r="L493" s="9"/>
     </row>
     <row r="494" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A494" s="11"/>
+      <c r="A494" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B494" s="4" t="s">
-        <v>656</v>
+        <v>568</v>
       </c>
       <c r="L494" s="9"/>
     </row>
     <row r="495" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B495" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="C495" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="D495" s="13" t="s">
-        <v>424</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="L495" s="9"/>
     </row>
     <row r="496" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B496" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="C496" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="D496" s="13" t="s">
-        <v>659</v>
-      </c>
-      <c r="F496" s="10" t="s">
-        <v>447</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="L496" s="9"/>
     </row>
     <row r="497" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A497" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B497" s="4" t="s">
-        <v>658</v>
+        <v>571</v>
       </c>
       <c r="D497" s="13" t="s">
-        <v>659</v>
-      </c>
-      <c r="L497" s="9" t="s">
-        <v>618</v>
+        <v>402</v>
       </c>
     </row>
     <row r="498" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A498" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B498" s="4" t="s">
-        <v>188</v>
-      </c>
+      <c r="A498" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B498" s="4"/>
       <c r="D498" s="13" t="s">
-        <v>425</v>
-      </c>
-      <c r="E498" s="12"/>
-      <c r="F498" t="s">
-        <v>15</v>
-      </c>
-      <c r="L498" s="9" t="s">
-        <v>640</v>
+        <v>603</v>
+      </c>
+      <c r="F498" s="9" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="499" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A499" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B499" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="D499" s="13"/>
+        <v>573</v>
+      </c>
+      <c r="L499" s="9"/>
     </row>
     <row r="500" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A500" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B500" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="D500" s="13"/>
+        <v>574</v>
+      </c>
+      <c r="L500" s="9"/>
     </row>
     <row r="501" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A501" s="3" t="s">
-        <v>23</v>
+      <c r="A501" s="11" t="s">
+        <v>359</v>
       </c>
       <c r="B501" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D501" s="13"/>
+        <v>575</v>
+      </c>
+      <c r="L501" s="9"/>
     </row>
     <row r="502" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A502" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B502" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="D502" s="13"/>
-      <c r="E502" s="12" t="s">
-        <v>418</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="L502" s="9"/>
     </row>
     <row r="503" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B503" s="4" t="s">
-        <v>661</v>
-      </c>
-      <c r="C503" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D503" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="E503" s="12" t="s">
-        <v>420</v>
-      </c>
-      <c r="F503" t="s">
-        <v>15</v>
-      </c>
-      <c r="L503" s="9" t="s">
-        <v>671</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="L503" s="9"/>
     </row>
     <row r="504" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A504" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B504" s="4" t="s">
-        <v>662</v>
-      </c>
-      <c r="D504" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="E504" s="12" t="s">
-        <v>419</v>
-      </c>
-      <c r="F504" t="s">
-        <v>15</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="C504" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="L504" s="9"/>
     </row>
     <row r="505" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A505" s="3" t="s">
-        <v>12</v>
+      <c r="A505" s="11" t="s">
+        <v>214</v>
       </c>
       <c r="B505" s="4" t="s">
-        <v>663</v>
-      </c>
-      <c r="C505" s="10" t="s">
-        <v>91</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="L505" s="9"/>
     </row>
     <row r="506" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A506" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B506" s="4" t="s">
-        <v>192</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="L506" s="9"/>
     </row>
     <row r="507" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A507" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B507" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="C507" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="L507" t="s">
-        <v>58</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="C507" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="L507" s="9"/>
     </row>
     <row r="508" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A508" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="B508" s="4" t="s">
-        <v>664</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="L508" s="9"/>
     </row>
     <row r="509" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A509" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B509" s="4" t="s">
-        <v>665</v>
-      </c>
-      <c r="C509" s="10" t="s">
-        <v>193</v>
-      </c>
+        <v>582</v>
+      </c>
+      <c r="L509" s="9"/>
     </row>
     <row r="510" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A510" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B510" s="4" t="s">
-        <v>666</v>
-      </c>
-      <c r="C510" s="10" t="s">
-        <v>52</v>
-      </c>
+        <v>583</v>
+      </c>
+      <c r="L510" s="9"/>
     </row>
     <row r="511" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A511" s="11" t="s">
+        <v>206</v>
+      </c>
       <c r="B511" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="D511" s="14" t="s">
-        <v>191</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="L511" s="9"/>
     </row>
     <row r="512" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A512" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="B512" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="D512" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F512" t="s">
-        <v>15</v>
-      </c>
-      <c r="L512" t="s">
-        <v>194</v>
+        <v>585</v>
+      </c>
+      <c r="D512" s="13" t="s">
+        <v>603</v>
+      </c>
+      <c r="L512" s="9" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="513" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A513" s="11"/>
       <c r="B513" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="L513" t="s">
-        <v>27</v>
+        <v>586</v>
+      </c>
+      <c r="C513" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="D513" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="F513" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="G513" s="9"/>
+      <c r="L513" s="9" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="514" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A514" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="A514" s="11"/>
       <c r="B514" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="D514" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="L514" t="s">
-        <v>27</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="G514" s="9"/>
     </row>
     <row r="515" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A515" s="3" t="s">
-        <v>126</v>
-      </c>
+      <c r="A515" s="11"/>
       <c r="B515" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="D515" s="13" t="s">
-        <v>722</v>
-      </c>
-      <c r="F515" t="s">
-        <v>15</v>
-      </c>
-      <c r="I515" s="9" t="s">
-        <v>717</v>
-      </c>
-      <c r="L515" s="9" t="s">
-        <v>680</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="C515" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="G515" s="9"/>
+      <c r="L515" s="9"/>
     </row>
     <row r="516" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A516" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="B516" s="4"/>
-      <c r="C516" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="D516" s="13" t="s">
-        <v>723</v>
-      </c>
-      <c r="L516" s="9" t="s">
-        <v>724</v>
-      </c>
+      <c r="A516" s="11"/>
+      <c r="B516" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="L516" s="9"/>
     </row>
     <row r="517" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A517" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B517" s="4" t="s">
-        <v>719</v>
+        <v>464</v>
+      </c>
+      <c r="C517" s="10" t="s">
+        <v>156</v>
       </c>
       <c r="D517" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="F517" t="s">
-        <v>15</v>
-      </c>
-      <c r="I517" s="9" t="s">
-        <v>720</v>
-      </c>
-      <c r="L517" s="9" t="s">
-        <v>721</v>
+        <v>384</v>
       </c>
     </row>
     <row r="518" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A518" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B518" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="F518" t="s">
-        <v>15</v>
-      </c>
-      <c r="I518" s="9"/>
-      <c r="L518" s="9" t="s">
-        <v>514</v>
+        <v>589</v>
+      </c>
+      <c r="C518" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="D518" s="13" t="s">
+        <v>591</v>
+      </c>
+      <c r="F518" s="10" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="519" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B519" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="I519" s="9"/>
-      <c r="L519" s="9"/>
+        <v>590</v>
+      </c>
+      <c r="D519" s="13" t="s">
+        <v>591</v>
+      </c>
+      <c r="L519" s="9" t="s">
+        <v>550</v>
+      </c>
     </row>
     <row r="520" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A520" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B520" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D520" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="E520" s="12"/>
+      <c r="F520" t="s">
+        <v>15</v>
+      </c>
       <c r="L520" s="9" t="s">
-        <v>202</v>
+        <v>572</v>
+      </c>
+    </row>
+    <row r="521" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A521" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B521" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="D521" s="13"/>
+    </row>
+    <row r="522" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A522" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B522" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D522" s="13"/>
+    </row>
+    <row r="523" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A523" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B523" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D523" s="13"/>
+    </row>
+    <row r="524" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A524" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B524" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="D524" s="13"/>
+      <c r="E524" s="12" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="525" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B525" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="C525" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D525" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="E525" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="F525" t="s">
+        <v>15</v>
+      </c>
+      <c r="L525" s="9" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="526" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B526" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="D526" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="E526" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="F526" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="527" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A527" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B527" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="C527" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="528" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A528" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B528" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="529" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A529" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B529" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C529" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="L529" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="530" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A530" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B530" s="4" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="531" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A531" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B531" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="C531" s="12" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="532" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B532" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="C532" s="12" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="533" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B533" s="4" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="534" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B534" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="D534" s="14" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="535" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B535" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="D535" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F535" t="s">
+        <v>15</v>
+      </c>
+      <c r="L535" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="536" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B536" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="L536" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="537" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A537" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B537" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="D537" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="L537" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="538" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A538" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B538" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="D538" s="13" t="s">
+        <v>651</v>
+      </c>
+      <c r="F538" t="s">
+        <v>15</v>
+      </c>
+      <c r="I538" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L538" s="9" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="539" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A539" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B539" s="4"/>
+      <c r="C539" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="D539" s="13" t="s">
+        <v>652</v>
+      </c>
+      <c r="L539" s="9" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="540" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A540" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B540" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="D540" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F540" t="s">
+        <v>15</v>
+      </c>
+      <c r="I540" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L540" s="9" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="541" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A541" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B541" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="D541" s="13"/>
+      <c r="I541" s="9"/>
+      <c r="L541" s="9"/>
+    </row>
+    <row r="542" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A542" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B542" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="F542" t="s">
+        <v>15</v>
+      </c>
+      <c r="I542" s="9"/>
+      <c r="L542" s="9" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="543" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B543" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="I543" s="9"/>
+      <c r="L543" s="9"/>
+    </row>
+    <row r="544" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A544" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B544" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="I544" s="9"/>
+      <c r="L544" s="9"/>
+    </row>
+    <row r="545" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B545" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="I545" s="9"/>
+      <c r="L545" s="9"/>
+    </row>
+    <row r="546" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B546" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="I546" s="9"/>
+      <c r="L546" s="9"/>
+    </row>
+    <row r="547" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B547" s="4"/>
+      <c r="I547" s="9"/>
+      <c r="L547" s="9"/>
+    </row>
+    <row r="548" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="I548" s="9"/>
+      <c r="L548" s="9"/>
+    </row>
+    <row r="549" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L549" s="9" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Chapter/Chapter4.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FFF0A2-9A68-4C98-84F7-6DB808875ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167088A9-E3C7-4800-9CF3-60A0DC422503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,9 +132,6 @@
   </si>
   <si>
     <t>你还是别发誓了，我怕好吧……</t>
-  </si>
-  <si>
-    <t>三人看见黑洞下有一个空心的光圈，那个光圈频繁抽搐，发射的光忽暗忽明。</t>
   </si>
   <si>
     <t>&lt;中心文本&gt;&lt;淡入&gt;为了确认情况，FoxTi三人跑了过去</t>
@@ -3361,6 +3358,10 @@
   </si>
   <si>
     <t>&lt;淡入&gt;&lt;中心文本&gt;正在前往漠寒线</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>三人看见不远处有一个空心的光圈，那个光圈频繁抽搐，发射的光忽暗忽明。</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -3868,25 +3869,25 @@
         <v>12</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B3" s="9" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="13"/>
@@ -3898,70 +3899,70 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" s="9" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D4" s="13"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B5" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D5" s="13"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B7" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B8" s="9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B9" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B10" s="9" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -3969,13 +3970,13 @@
         <v>12</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
@@ -3987,7 +3988,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D12" s="13"/>
       <c r="I12" s="7"/>
@@ -3997,7 +3998,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D13" s="13"/>
       <c r="I13" s="7"/>
@@ -4007,7 +4008,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D14" s="13"/>
       <c r="I14" s="7"/>
@@ -4017,7 +4018,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D15" s="13"/>
     </row>
@@ -4062,7 +4063,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D20" s="13"/>
     </row>
@@ -4071,7 +4072,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D21" s="13"/>
     </row>
@@ -4080,7 +4081,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D22" s="13"/>
     </row>
@@ -4089,7 +4090,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D23" s="13"/>
     </row>
@@ -4098,7 +4099,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D24" s="13"/>
     </row>
@@ -4107,7 +4108,7 @@
         <v>12</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D25" s="13"/>
     </row>
@@ -4116,7 +4117,7 @@
         <v>19</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D26" s="13"/>
     </row>
@@ -4125,10 +4126,10 @@
         <v>22</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>16</v>
@@ -4142,7 +4143,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>13</v>
@@ -4202,11 +4203,11 @@
       <c r="A33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B33" t="s">
-        <v>33</v>
+      <c r="B33" s="9" t="s">
+        <v>745</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>29</v>
@@ -4215,7 +4216,7 @@
         <v>17</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
@@ -4223,10 +4224,10 @@
         <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D34" s="14" t="s">
         <v>13</v>
@@ -4238,21 +4239,21 @@
         <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="14" t="s">
         <v>37</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>38</v>
       </c>
       <c r="F35" t="s">
         <v>17</v>
       </c>
       <c r="K35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
@@ -4260,10 +4261,10 @@
         <v>19</v>
       </c>
       <c r="B36" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" t="s">
         <v>40</v>
-      </c>
-      <c r="I36" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
@@ -4271,10 +4272,10 @@
         <v>12</v>
       </c>
       <c r="B37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>42</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
@@ -4282,15 +4283,15 @@
         <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" t="s">
         <v>45</v>
-      </c>
-      <c r="B39" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
@@ -4298,59 +4299,59 @@
         <v>12</v>
       </c>
       <c r="B40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="10" t="s">
         <v>47</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D44" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F44" t="s">
         <v>52</v>
       </c>
-      <c r="F44" t="s">
+      <c r="L44" t="s">
         <v>53</v>
-      </c>
-      <c r="L44" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>14</v>
@@ -4358,64 +4359,64 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F46" t="s">
         <v>17</v>
       </c>
       <c r="L46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B47" s="9" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F47" t="s">
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B48" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B49" s="9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B50" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B51" s="9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B52" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
@@ -4423,10 +4424,10 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
@@ -4434,7 +4435,7 @@
         <v>18</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
@@ -4442,7 +4443,7 @@
         <v>12</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
@@ -4450,7 +4451,7 @@
         <v>18</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
@@ -4458,32 +4459,32 @@
         <v>12</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L57" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K58" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L58" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
@@ -4491,31 +4492,28 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
+        <v>63</v>
+      </c>
+      <c r="I60" t="s">
         <v>64</v>
       </c>
-      <c r="I60" t="s">
+      <c r="L60" t="s">
         <v>65</v>
-      </c>
-      <c r="L60" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>69</v>
-      </c>
-      <c r="L63" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
@@ -4523,7 +4521,7 @@
         <v>12</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
@@ -4531,23 +4529,26 @@
         <v>18</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>668</v>
+        <v>667</v>
+      </c>
+      <c r="L67" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
@@ -4556,7 +4557,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
@@ -4564,26 +4565,26 @@
         <v>12</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="I70" t="s">
+        <v>70</v>
+      </c>
+      <c r="L70" t="s">
         <v>71</v>
-      </c>
-      <c r="L70" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B71" s="9" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="L71" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
@@ -4591,31 +4592,31 @@
         <v>19</v>
       </c>
       <c r="B73" t="s">
+        <v>72</v>
+      </c>
+      <c r="I73" t="s">
         <v>73</v>
       </c>
-      <c r="I73" t="s">
+      <c r="L73" t="s">
         <v>74</v>
-      </c>
-      <c r="L73" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L75" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
@@ -4623,36 +4624,36 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
+        <v>77</v>
+      </c>
+      <c r="I77" t="s">
         <v>78</v>
       </c>
-      <c r="I77" t="s">
+      <c r="L77" t="s">
         <v>79</v>
-      </c>
-      <c r="L77" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B79" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B80" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L80" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
@@ -4660,16 +4661,16 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C82" s="10" t="s">
+      <c r="I82" t="s">
         <v>85</v>
       </c>
-      <c r="I82" t="s">
+      <c r="L82" t="s">
         <v>86</v>
-      </c>
-      <c r="L82" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
@@ -4677,7 +4678,7 @@
         <v>19</v>
       </c>
       <c r="B83" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
@@ -4685,23 +4686,23 @@
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L84" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B86" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I86" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
@@ -4709,25 +4710,25 @@
         <v>12</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I88" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B89" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B90" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B91" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
@@ -4735,7 +4736,7 @@
         <v>12</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
@@ -4743,7 +4744,7 @@
         <v>18</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
@@ -4751,18 +4752,18 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B95" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
@@ -4770,35 +4771,35 @@
         <v>12</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D96" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L96" t="s">
         <v>58</v>
-      </c>
-      <c r="L96" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B97" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F97" t="s">
         <v>17</v>
       </c>
       <c r="L97" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B98" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
@@ -4806,7 +4807,7 @@
         <v>12</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
@@ -4814,7 +4815,7 @@
         <v>22</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
@@ -4822,7 +4823,7 @@
         <v>12</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
@@ -4830,7 +4831,7 @@
         <v>19</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
@@ -4838,7 +4839,7 @@
         <v>12</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.2">
@@ -4846,10 +4847,10 @@
         <v>12</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
@@ -4857,7 +4858,7 @@
         <v>22</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
@@ -4865,7 +4866,7 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
@@ -4873,26 +4874,26 @@
         <v>12</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="L108" t="s">
         <v>98</v>
-      </c>
-      <c r="B108" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="L108" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B109" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
@@ -4900,7 +4901,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
@@ -4908,7 +4909,7 @@
         <v>19</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
@@ -4916,7 +4917,7 @@
         <v>18</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
@@ -4924,7 +4925,7 @@
         <v>22</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
@@ -4932,7 +4933,7 @@
         <v>12</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
@@ -4940,26 +4941,26 @@
         <v>12</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="B117" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
@@ -4967,24 +4968,24 @@
         <v>22</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" s="11" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B119" t="s">
+        <v>101</v>
+      </c>
+      <c r="C119" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="C119" s="10" t="s">
+      <c r="E119" s="10" t="s">
         <v>103</v>
-      </c>
-      <c r="E119" s="10" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
@@ -4992,18 +4993,18 @@
         <v>12</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C121" s="12"/>
     </row>
@@ -5012,7 +5013,7 @@
         <v>12</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C122" s="12"/>
     </row>
@@ -5021,34 +5022,34 @@
         <v>12</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C123" s="12"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" s="11" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C124" s="12"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" s="11" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C125" s="12"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="11" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C126" s="12"/>
     </row>
@@ -5057,7 +5058,7 @@
         <v>12</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C127" s="12"/>
     </row>
@@ -5066,7 +5067,7 @@
         <v>18</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C128" s="12"/>
     </row>
@@ -5075,21 +5076,21 @@
         <v>12</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C129" s="12"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B130" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B131" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
@@ -5097,24 +5098,24 @@
         <v>12</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F132" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
@@ -5122,18 +5123,18 @@
         <v>12</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="B135" s="4" t="s">
         <v>214</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
@@ -5141,49 +5142,49 @@
         <v>12</v>
       </c>
       <c r="B136" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C136" s="12" t="s">
         <v>417</v>
       </c>
-      <c r="C136" s="12" t="s">
-        <v>418</v>
-      </c>
       <c r="D136" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B137" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C137" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="C137" s="12" t="s">
-        <v>217</v>
-      </c>
       <c r="D137" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F137" t="s">
         <v>17</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B138" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G138" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B139" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
@@ -5191,7 +5192,7 @@
         <v>12</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
@@ -5199,7 +5200,7 @@
         <v>19</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
@@ -5207,7 +5208,7 @@
         <v>12</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
@@ -5215,15 +5216,15 @@
         <v>22</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
@@ -5231,10 +5232,10 @@
         <v>19</v>
       </c>
       <c r="B145" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C145" s="12" t="s">
         <v>227</v>
-      </c>
-      <c r="C145" s="12" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
@@ -5242,7 +5243,7 @@
         <v>12</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C146" s="12"/>
     </row>
@@ -5251,7 +5252,7 @@
         <v>18</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
@@ -5259,7 +5260,7 @@
         <v>22</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.2">
@@ -5267,7 +5268,7 @@
         <v>12</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.2">
@@ -5275,7 +5276,7 @@
         <v>18</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.2">
@@ -5283,49 +5284,49 @@
         <v>12</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B152" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D152" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E152" s="12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B153" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D153" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E153" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L153" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B154" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D154" s="13" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E154" s="12" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
@@ -5333,13 +5334,13 @@
         <v>12</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D155" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F155" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
@@ -5347,16 +5348,16 @@
         <v>19</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D156" s="13" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F156" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H156" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
@@ -5364,18 +5365,18 @@
         <v>12</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H158" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
@@ -5383,40 +5384,40 @@
         <v>12</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D160" s="13" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E160" s="12"/>
       <c r="H160" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="B161" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="B161" s="4" t="s">
-        <v>250</v>
-      </c>
       <c r="D161" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E161" s="12"/>
       <c r="F161" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
@@ -5424,17 +5425,17 @@
         <v>22</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C162" s="12" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D162" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E162" s="12"/>
       <c r="F162" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
@@ -5442,27 +5443,27 @@
         <v>12</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B164" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B165" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B166" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B167" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
@@ -5470,7 +5471,7 @@
         <v>12</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
@@ -5478,15 +5479,15 @@
         <v>18</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
@@ -5494,15 +5495,15 @@
         <v>12</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
@@ -5510,15 +5511,15 @@
         <v>12</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
@@ -5526,29 +5527,29 @@
         <v>12</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C177" s="12" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
@@ -5556,18 +5557,18 @@
         <v>12</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C179" s="12"/>
     </row>
@@ -5576,15 +5577,15 @@
         <v>12</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A181" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
@@ -5592,23 +5593,23 @@
         <v>12</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A184" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
@@ -5616,15 +5617,15 @@
         <v>12</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A186" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
@@ -5632,18 +5633,18 @@
         <v>12</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C187" s="12" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A188" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
@@ -5651,31 +5652,31 @@
         <v>12</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A190" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A191" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A192" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.2">
@@ -5683,15 +5684,15 @@
         <v>12</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A194" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.2">
@@ -5699,15 +5700,15 @@
         <v>12</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A196" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
@@ -5715,17 +5716,17 @@
         <v>12</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B198" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B199" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
@@ -5733,139 +5734,139 @@
         <v>12</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C200" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A201" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C201" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A202" s="11"/>
       <c r="B202" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C202" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A203" s="11"/>
       <c r="B203" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C203" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A204" s="11"/>
       <c r="B204" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C204" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A205" s="11"/>
       <c r="B205" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C205" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A206" s="11"/>
       <c r="B206" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C206" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A207" s="11"/>
       <c r="B207" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C207" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A208" s="11"/>
       <c r="B208" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C208" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A209" s="11"/>
       <c r="B209" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C209" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A210" s="11"/>
       <c r="B210" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C210" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="11"/>
       <c r="B211" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C211" s="11" t="s">
         <v>276</v>
-      </c>
-      <c r="C211" s="11" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A212" s="11"/>
       <c r="B212" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C212" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A213" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C213" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A214" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
@@ -5873,7 +5874,7 @@
         <v>12</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
@@ -5881,15 +5882,15 @@
         <v>19</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A217" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.2">
@@ -5897,7 +5898,7 @@
         <v>19</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
@@ -5905,7 +5906,7 @@
         <v>12</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -5913,7 +5914,7 @@
         <v>19</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
@@ -5921,7 +5922,7 @@
         <v>12</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
@@ -5929,7 +5930,7 @@
         <v>22</v>
       </c>
       <c r="B222" s="8" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.2">
@@ -5937,7 +5938,7 @@
         <v>12</v>
       </c>
       <c r="B223" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.2">
@@ -5945,18 +5946,18 @@
         <v>19</v>
       </c>
       <c r="B224" s="8" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A225" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C225" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.2">
@@ -5964,15 +5965,15 @@
         <v>12</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A227" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.2">
@@ -5980,21 +5981,21 @@
         <v>12</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A229" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D229" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E229" s="12" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.2">
@@ -6002,50 +6003,50 @@
         <v>12</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D230" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E230" s="12" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="F230" t="s">
         <v>15</v>
       </c>
       <c r="L230" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B231" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E231" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B232" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E232" s="12"/>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B233" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E233" s="12"/>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B234" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E234" s="12"/>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B235" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E235" s="12"/>
     </row>
@@ -6054,10 +6055,10 @@
         <v>12</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C236" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D236" s="14" t="s">
         <v>13</v>
@@ -6068,10 +6069,10 @@
         <v>18</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D237" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F237" t="s">
         <v>15</v>
@@ -6082,7 +6083,7 @@
         <v>12</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.2">
@@ -6090,10 +6091,10 @@
         <v>19</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D239" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.2">
@@ -6101,7 +6102,7 @@
         <v>18</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.2">
@@ -6109,7 +6110,7 @@
         <v>22</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.2">
@@ -6117,7 +6118,7 @@
         <v>19</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.2">
@@ -6125,26 +6126,26 @@
         <v>12</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B244" s="4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A245" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C245" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D245" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F245" t="s">
         <v>17</v>
@@ -6153,30 +6154,30 @@
     <row r="246" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A246" s="11"/>
       <c r="B246" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A247" s="11"/>
       <c r="B247" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A248" s="11"/>
       <c r="B248" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A249" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C249" s="12" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.2">
@@ -6184,7 +6185,7 @@
         <v>22</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.2">
@@ -6192,7 +6193,7 @@
         <v>12</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.2">
@@ -6200,7 +6201,7 @@
         <v>22</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.2">
@@ -6208,7 +6209,7 @@
         <v>19</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.2">
@@ -6216,7 +6217,7 @@
         <v>12</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.2">
@@ -6224,7 +6225,7 @@
         <v>19</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.2">
@@ -6232,13 +6233,13 @@
         <v>12</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D256" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E256" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.2">
@@ -6246,16 +6247,16 @@
         <v>12</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D257" s="13" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E257" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F257" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.2">
@@ -6263,7 +6264,7 @@
         <v>18</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.2">
@@ -6271,26 +6272,26 @@
         <v>12</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A260" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C260" s="12" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A261" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.2">
@@ -6298,7 +6299,7 @@
         <v>12</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.2">
@@ -6306,7 +6307,7 @@
         <v>19</v>
       </c>
       <c r="B263" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.2">
@@ -6314,7 +6315,7 @@
         <v>12</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.2">
@@ -6322,7 +6323,7 @@
         <v>18</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.2">
@@ -6330,7 +6331,7 @@
         <v>12</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.2">
@@ -6338,20 +6339,20 @@
         <v>19</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L267" s="9" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B268" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B269" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.2">
@@ -6359,7 +6360,7 @@
         <v>19</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.2">
@@ -6367,26 +6368,26 @@
         <v>12</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G271" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B272" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G272" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L272" s="9" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B273" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.2">
@@ -6394,15 +6395,15 @@
         <v>12</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A275" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.2">
@@ -6410,37 +6411,37 @@
         <v>12</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A277" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A278" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A279" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C279" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L279" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.2">
@@ -6448,34 +6449,34 @@
         <v>12</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B281" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C281" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B282" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="C282" s="12" t="s">
         <v>436</v>
       </c>
-      <c r="C282" s="12" t="s">
-        <v>437</v>
-      </c>
       <c r="L282" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B283" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C283" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.2">
@@ -6483,24 +6484,24 @@
         <v>12</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C284" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A285" s="11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B285" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C285" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="C285" s="10" t="s">
+      <c r="G285" t="s">
         <v>118</v>
-      </c>
-      <c r="G285" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.2">
@@ -6508,13 +6509,13 @@
         <v>12</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C286" s="12" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G286" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.2">
@@ -6522,19 +6523,19 @@
         <v>12</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C287" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A288" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B288" s="4"/>
       <c r="C288" s="12" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.2">
@@ -6542,7 +6543,7 @@
         <v>12</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C289" s="12"/>
     </row>
@@ -6551,10 +6552,10 @@
         <v>12</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C290" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.2">
@@ -6562,10 +6563,10 @@
         <v>19</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G291" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.2">
@@ -6573,7 +6574,7 @@
         <v>12</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.2">
@@ -6581,15 +6582,15 @@
         <v>19</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A294" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.2">
@@ -6597,7 +6598,7 @@
         <v>19</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.2">
@@ -6605,7 +6606,7 @@
         <v>12</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.2">
@@ -6613,7 +6614,7 @@
         <v>19</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.2">
@@ -6621,10 +6622,10 @@
         <v>12</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C298" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.2">
@@ -6632,7 +6633,7 @@
         <v>19</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.2">
@@ -6640,7 +6641,7 @@
         <v>18</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.2">
@@ -6648,26 +6649,26 @@
         <v>12</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B302" s="4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C302" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B303" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D303" s="13" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E303" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.2">
@@ -6675,16 +6676,16 @@
         <v>12</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C304" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D304" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D304" s="14" t="s">
-        <v>125</v>
-      </c>
       <c r="E304" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F304" t="s">
         <v>15</v>
@@ -6692,10 +6693,10 @@
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A305" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.2">
@@ -6703,7 +6704,7 @@
         <v>19</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.2">
@@ -6711,21 +6712,21 @@
         <v>12</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B308" s="4" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C308" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D308" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E308" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F308" t="s">
         <v>17</v>
@@ -6733,7 +6734,7 @@
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B309" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.2">
@@ -6741,7 +6742,7 @@
         <v>12</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.2">
@@ -6749,16 +6750,16 @@
         <v>18</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A312" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B312" s="4"/>
       <c r="K312" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.2">
@@ -6766,33 +6767,33 @@
         <v>12</v>
       </c>
       <c r="B313" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D313" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="E313" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="I313" t="s">
         <v>131</v>
-      </c>
-      <c r="D313" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="E313" s="10" t="s">
-        <v>623</v>
-      </c>
-      <c r="I313" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A314" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D314" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E314" s="12" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F314" t="s">
         <v>15</v>
@@ -6801,44 +6802,44 @@
     <row r="315" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A315" s="11"/>
       <c r="B315" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C315" s="3"/>
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A316" s="11"/>
       <c r="B316" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C316" s="3"/>
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A317" s="11"/>
       <c r="B317" s="4" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C317" s="3"/>
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A318" s="11"/>
       <c r="B318" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C318" s="3"/>
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A319" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C319" s="3"/>
       <c r="D319" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E319" s="12" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.2">
@@ -6846,13 +6847,13 @@
         <v>12</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D320" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E320" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F320" t="s">
         <v>15</v>
@@ -6860,46 +6861,46 @@
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B321" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C321" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B322" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B323" s="4" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B324" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B325" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B326" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B327" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D327" s="13" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E327" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.2">
@@ -6907,13 +6908,13 @@
         <v>12</v>
       </c>
       <c r="B328" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="D328" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="E328" s="12" t="s">
         <v>729</v>
-      </c>
-      <c r="D328" s="13" t="s">
-        <v>389</v>
-      </c>
-      <c r="E328" s="12" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="329" spans="1:12" x14ac:dyDescent="0.2">
@@ -6921,7 +6922,7 @@
         <v>12</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D329" s="13"/>
       <c r="E329" s="12"/>
@@ -6931,26 +6932,26 @@
         <v>12</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C330" s="12" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I330" s="9"/>
     </row>
     <row r="331" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A331" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B331" s="4"/>
       <c r="C331" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D331" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E331" s="12" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F331" t="s">
         <v>15</v>
@@ -6961,26 +6962,26 @@
         <v>12</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="333" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A333" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C333" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A334" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B334" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="B334" s="4" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="335" spans="1:12" x14ac:dyDescent="0.2">
@@ -6988,22 +6989,22 @@
         <v>12</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L335" s="9" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A336" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B336" s="4"/>
       <c r="C336" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L336" s="9" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.2">
@@ -7011,7 +7012,7 @@
         <v>12</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="338" spans="1:12" x14ac:dyDescent="0.2">
@@ -7019,7 +7020,7 @@
         <v>18</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="339" spans="1:12" x14ac:dyDescent="0.2">
@@ -7027,7 +7028,7 @@
         <v>12</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.2">
@@ -7035,10 +7036,10 @@
         <v>22</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E340" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.2">
@@ -7046,19 +7047,19 @@
         <v>12</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C341" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D341" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E341" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="L341" s="9" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.2">
@@ -7066,16 +7067,16 @@
         <v>12</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D342" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F342" t="s">
         <v>15</v>
       </c>
       <c r="L342" s="9" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="343" spans="1:12" x14ac:dyDescent="0.2">
@@ -7083,18 +7084,18 @@
         <v>19</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A344" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B344" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C344" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="C344" s="10" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="345" spans="1:12" x14ac:dyDescent="0.2">
@@ -7102,7 +7103,7 @@
         <v>19</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.2">
@@ -7110,37 +7111,37 @@
         <v>12</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="347" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A347" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B347" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C347" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="C347" s="10" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B348" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C348" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="C348" s="10" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="349" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A349" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C349" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.2">
@@ -7148,15 +7149,15 @@
         <v>12</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C350" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B351" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.2">
@@ -7164,7 +7165,7 @@
         <v>12</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.2">
@@ -7172,7 +7173,7 @@
         <v>19</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.2">
@@ -7180,15 +7181,15 @@
         <v>12</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A355" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.2">
@@ -7196,15 +7197,15 @@
         <v>12</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A357" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.2">
@@ -7212,7 +7213,7 @@
         <v>12</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.2">
@@ -7220,10 +7221,10 @@
         <v>19</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D359" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.2">
@@ -7231,13 +7232,13 @@
         <v>12</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D360" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F360" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.2">
@@ -7245,7 +7246,7 @@
         <v>12</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.2">
@@ -7253,7 +7254,7 @@
         <v>19</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.2">
@@ -7261,22 +7262,22 @@
         <v>12</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D363" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A364" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B364" s="4"/>
       <c r="D364" s="13" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F364" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.2">
@@ -7284,7 +7285,7 @@
         <v>12</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D365" s="13"/>
       <c r="F365" s="9"/>
@@ -7294,24 +7295,24 @@
         <v>12</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D366" s="13" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A367" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D367" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F367" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.2">
@@ -7319,15 +7320,15 @@
         <v>19</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A369" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.2">
@@ -7335,18 +7336,18 @@
         <v>12</v>
       </c>
       <c r="B370" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C370" s="12" t="s">
         <v>522</v>
-      </c>
-      <c r="C370" s="12" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A371" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.2">
@@ -7354,39 +7355,39 @@
         <v>12</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A373" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A374" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A375" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.2">
@@ -7394,7 +7395,7 @@
         <v>12</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.2">
@@ -7402,15 +7403,15 @@
         <v>12</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A379" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.2">
@@ -7418,23 +7419,23 @@
         <v>12</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A381" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A382" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.2">
@@ -7442,12 +7443,12 @@
         <v>12</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B384" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.2">
@@ -7455,18 +7456,18 @@
         <v>12</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="386" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A386" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D386" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.2">
@@ -7474,21 +7475,21 @@
         <v>12</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D387" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F387" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="388" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B388" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D388" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F388" t="s">
         <v>17</v>
@@ -7496,43 +7497,43 @@
     </row>
     <row r="389" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B389" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L389" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="390" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B390" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="L390" t="s">
         <v>152</v>
-      </c>
-      <c r="L390" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="391" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B391" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B392" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="393" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B393" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="394" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B394" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="395" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B395" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="396" spans="1:12" x14ac:dyDescent="0.2">
@@ -7540,21 +7541,21 @@
         <v>12</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L396" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="397" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A397" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L397" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="398" spans="1:12" x14ac:dyDescent="0.2">
@@ -7562,21 +7563,21 @@
         <v>12</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E398" s="12" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A399" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E399" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="400" spans="1:12" x14ac:dyDescent="0.2">
@@ -7584,10 +7585,10 @@
         <v>22</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E400" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="401" spans="1:12" x14ac:dyDescent="0.2">
@@ -7595,71 +7596,71 @@
         <v>12</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="402" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B402" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="L402" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="403" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B403" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D403" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E403" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="404" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B404" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C404" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D404" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E404" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L404" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="405" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B405" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D405" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E405" s="12" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="406" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B406" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D406" s="13" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E406" s="12"/>
       <c r="F406" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="407" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B407" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L407" s="9"/>
     </row>
@@ -7668,31 +7669,31 @@
         <v>12</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D408" s="13" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I408" s="9" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="L408" s="9" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="409" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A409" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B409" s="4"/>
       <c r="C409" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D409" s="12" t="s">
+        <v>641</v>
+      </c>
+      <c r="L409" s="9" t="s">
         <v>642</v>
-      </c>
-      <c r="L409" s="9" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="410" spans="1:12" x14ac:dyDescent="0.2">
@@ -7700,27 +7701,27 @@
         <v>12</v>
       </c>
       <c r="B410" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="C410" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="C410" s="12" t="s">
-        <v>451</v>
-      </c>
       <c r="D410" s="13" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I410" s="9" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="L410" s="9" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="411" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A411" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="412" spans="1:12" x14ac:dyDescent="0.2">
@@ -7728,28 +7729,28 @@
         <v>12</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="413" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B413" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="414" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B414" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C414" s="12" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="415" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A415" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="416" spans="1:12" x14ac:dyDescent="0.2">
@@ -7757,15 +7758,15 @@
         <v>12</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="417" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A417" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D417" s="13"/>
       <c r="I417" s="9"/>
@@ -7775,23 +7776,23 @@
         <v>12</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C418" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I418" s="9"/>
       <c r="L418" s="9"/>
     </row>
     <row r="419" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A419" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D419" s="13" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="420" spans="1:12" x14ac:dyDescent="0.2">
@@ -7799,21 +7800,21 @@
         <v>12</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C420" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D420" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F420" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="421" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B421" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C421" s="12"/>
       <c r="D421" s="13"/>
@@ -7823,19 +7824,19 @@
         <v>12</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F422" s="9"/>
     </row>
     <row r="423" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A423" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D423" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="424" spans="1:12" x14ac:dyDescent="0.2">
@@ -7843,68 +7844,68 @@
         <v>12</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D424" s="13" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F424" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="425" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B425" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="426" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B426" s="4" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="427" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B427" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D427" s="13" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="428" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B428" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C428" s="12" t="s">
+        <v>639</v>
+      </c>
+      <c r="D428" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="C428" s="12" t="s">
-        <v>640</v>
-      </c>
-      <c r="D428" s="13" t="s">
-        <v>350</v>
-      </c>
       <c r="E428" s="12" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F428" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="429" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A429" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C429" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D429" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E429" s="12" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F429" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="430" spans="1:12" x14ac:dyDescent="0.2">
@@ -7912,7 +7913,7 @@
         <v>19</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="431" spans="1:12" x14ac:dyDescent="0.2">
@@ -7920,7 +7921,7 @@
         <v>12</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="432" spans="1:12" x14ac:dyDescent="0.2">
@@ -7928,7 +7929,7 @@
         <v>19</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D432" s="13"/>
       <c r="E432" s="12"/>
@@ -7939,26 +7940,26 @@
         <v>12</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D433" s="13"/>
       <c r="E433" s="12"/>
       <c r="F433" s="9"/>
       <c r="G433" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B434" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G434" s="9" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B435" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.2">
@@ -7966,35 +7967,35 @@
         <v>12</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A437" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B437" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B437" s="4" t="s">
-        <v>158</v>
-      </c>
       <c r="C437" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H437" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A438" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C438" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H438" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.2">
@@ -8002,35 +8003,35 @@
         <v>19</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A440" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C440" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H440" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A441" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B441" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B441" s="4" t="s">
-        <v>162</v>
-      </c>
       <c r="C441" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H441" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.2">
@@ -8038,7 +8039,7 @@
         <v>19</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.2">
@@ -8046,7 +8047,7 @@
         <v>12</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.2">
@@ -8054,21 +8055,21 @@
         <v>12</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G444" s="9" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A445" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G445" s="9" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.2">
@@ -8076,10 +8077,10 @@
         <v>12</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C446" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.2">
@@ -8087,7 +8088,7 @@
         <v>19</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.2">
@@ -8095,15 +8096,15 @@
         <v>12</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A449" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.2">
@@ -8111,7 +8112,7 @@
         <v>12</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.2">
@@ -8119,7 +8120,7 @@
         <v>19</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.2">
@@ -8127,18 +8128,18 @@
         <v>12</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C452" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A453" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.2">
@@ -8146,55 +8147,55 @@
         <v>19</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A455" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A456" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A457" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A458" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A459" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A460" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.2">
@@ -8202,26 +8203,26 @@
         <v>12</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A462" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A463" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G463" s="9" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.2">
@@ -8229,10 +8230,10 @@
         <v>12</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G464" s="9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="465" spans="1:12" x14ac:dyDescent="0.2">
@@ -8240,18 +8241,18 @@
         <v>12</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="466" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A466" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G466" s="9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="467" spans="1:12" x14ac:dyDescent="0.2">
@@ -8259,13 +8260,13 @@
         <v>12</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C467" s="12" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G467" s="9" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="468" spans="1:12" x14ac:dyDescent="0.2">
@@ -8273,21 +8274,21 @@
         <v>19</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="469" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A469" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D469" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G469" s="9" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="470" spans="1:12" x14ac:dyDescent="0.2">
@@ -8295,16 +8296,16 @@
         <v>12</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C470" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D470" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G470" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="471" spans="1:12" x14ac:dyDescent="0.2">
@@ -8312,42 +8313,42 @@
         <v>12</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C471" s="12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D471" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E471" s="12" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G471" s="9" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="472" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A472" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D472" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E472" s="12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F472" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G472" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L472" s="9" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="473" spans="1:12" x14ac:dyDescent="0.2">
@@ -8355,7 +8356,7 @@
         <v>12</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D473" s="13"/>
       <c r="E473" s="12"/>
@@ -8364,7 +8365,7 @@
     </row>
     <row r="474" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B474" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D474" s="13"/>
       <c r="E474" s="12"/>
@@ -8376,7 +8377,7 @@
         <v>12</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D475" s="13"/>
       <c r="E475" s="12"/>
@@ -8388,15 +8389,15 @@
         <v>19</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="477" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A477" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L477" s="9"/>
     </row>
@@ -8405,7 +8406,7 @@
         <v>12</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L478" s="9"/>
     </row>
@@ -8414,16 +8415,16 @@
         <v>19</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="L479" s="9"/>
     </row>
     <row r="480" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A480" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="L480" s="9"/>
     </row>
@@ -8432,7 +8433,7 @@
         <v>12</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="L481" s="9"/>
     </row>
@@ -8441,16 +8442,16 @@
         <v>12</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="L482" s="9"/>
     </row>
     <row r="483" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A483" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L483" s="9"/>
     </row>
@@ -8459,25 +8460,25 @@
         <v>12</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="L484" s="9"/>
     </row>
     <row r="485" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A485" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L485" s="9"/>
     </row>
     <row r="486" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A486" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="L486" s="9"/>
     </row>
@@ -8486,21 +8487,21 @@
         <v>12</v>
       </c>
       <c r="B487" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="L487" s="9"/>
     </row>
     <row r="488" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B488" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="L488" s="9" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="489" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B489" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="L489" s="9"/>
     </row>
@@ -8509,16 +8510,16 @@
         <v>12</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L490" s="9"/>
     </row>
     <row r="491" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A491" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="L491" s="9"/>
     </row>
@@ -8527,7 +8528,7 @@
         <v>12</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L492" s="9"/>
     </row>
@@ -8536,7 +8537,7 @@
         <v>19</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="L493" s="9"/>
     </row>
@@ -8545,19 +8546,19 @@
         <v>12</v>
       </c>
       <c r="B494" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L494" s="9"/>
     </row>
     <row r="495" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B495" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L495" s="9"/>
     </row>
     <row r="496" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B496" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="L496" s="9"/>
     </row>
@@ -8566,22 +8567,22 @@
         <v>12</v>
       </c>
       <c r="B497" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D497" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="498" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A498" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B498" s="4"/>
       <c r="D498" s="13" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F498" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="499" spans="1:12" x14ac:dyDescent="0.2">
@@ -8589,7 +8590,7 @@
         <v>12</v>
       </c>
       <c r="B499" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L499" s="9"/>
     </row>
@@ -8598,16 +8599,16 @@
         <v>12</v>
       </c>
       <c r="B500" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="L500" s="9"/>
     </row>
     <row r="501" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A501" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B501" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L501" s="9"/>
     </row>
@@ -8616,13 +8617,13 @@
         <v>12</v>
       </c>
       <c r="B502" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="L502" s="9"/>
     </row>
     <row r="503" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B503" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L503" s="9"/>
     </row>
@@ -8631,19 +8632,19 @@
         <v>12</v>
       </c>
       <c r="B504" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C504" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L504" s="9"/>
     </row>
     <row r="505" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A505" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B505" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="L505" s="9"/>
     </row>
@@ -8652,28 +8653,28 @@
         <v>12</v>
       </c>
       <c r="B506" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="L506" s="9"/>
     </row>
     <row r="507" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B507" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C507" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L507" s="9"/>
     </row>
     <row r="508" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B508" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="L508" s="9"/>
     </row>
     <row r="509" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B509" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="L509" s="9"/>
     </row>
@@ -8682,16 +8683,16 @@
         <v>12</v>
       </c>
       <c r="B510" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="L510" s="9"/>
     </row>
     <row r="511" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A511" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B511" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="L511" s="9"/>
     </row>
@@ -8700,48 +8701,48 @@
         <v>12</v>
       </c>
       <c r="B512" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D512" s="13" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="L512" s="9" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="513" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A513" s="11"/>
       <c r="B513" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C513" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D513" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F513" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G513" s="9"/>
       <c r="L513" s="9" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="514" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A514" s="11"/>
       <c r="B514" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G514" s="9"/>
     </row>
     <row r="515" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A515" s="11"/>
       <c r="B515" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C515" s="12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G515" s="9"/>
       <c r="L515" s="9"/>
@@ -8749,44 +8750,44 @@
     <row r="516" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A516" s="11"/>
       <c r="B516" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="L516" s="9"/>
     </row>
     <row r="517" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B517" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C517" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D517" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="518" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B518" s="4" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C518" s="12" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D518" s="13" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="F518" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="519" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B519" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="D519" s="13" t="s">
         <v>590</v>
       </c>
-      <c r="D519" s="13" t="s">
-        <v>591</v>
-      </c>
       <c r="L519" s="9" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="520" spans="1:12" x14ac:dyDescent="0.2">
@@ -8794,17 +8795,17 @@
         <v>12</v>
       </c>
       <c r="B520" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D520" s="13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E520" s="12"/>
       <c r="F520" t="s">
         <v>15</v>
       </c>
       <c r="L520" s="9" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="521" spans="1:12" x14ac:dyDescent="0.2">
@@ -8812,7 +8813,7 @@
         <v>19</v>
       </c>
       <c r="B521" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D521" s="13"/>
     </row>
@@ -8821,7 +8822,7 @@
         <v>12</v>
       </c>
       <c r="B522" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D522" s="13"/>
     </row>
@@ -8830,7 +8831,7 @@
         <v>22</v>
       </c>
       <c r="B523" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D523" s="13"/>
     </row>
@@ -8839,42 +8840,42 @@
         <v>12</v>
       </c>
       <c r="B524" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D524" s="13"/>
       <c r="E524" s="12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="525" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B525" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C525" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D525" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E525" s="12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F525" t="s">
         <v>15</v>
       </c>
       <c r="L525" s="9" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="526" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B526" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D526" s="13" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E526" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F526" t="s">
         <v>15</v>
@@ -8885,10 +8886,10 @@
         <v>12</v>
       </c>
       <c r="B527" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C527" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="528" spans="1:12" x14ac:dyDescent="0.2">
@@ -8896,7 +8897,7 @@
         <v>19</v>
       </c>
       <c r="B528" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="529" spans="1:12" x14ac:dyDescent="0.2">
@@ -8904,13 +8905,13 @@
         <v>12</v>
       </c>
       <c r="B529" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C529" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L529" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="530" spans="1:12" x14ac:dyDescent="0.2">
@@ -8918,7 +8919,7 @@
         <v>19</v>
       </c>
       <c r="B530" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="531" spans="1:12" x14ac:dyDescent="0.2">
@@ -8926,36 +8927,36 @@
         <v>12</v>
       </c>
       <c r="B531" s="4" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C531" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="532" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B532" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C532" s="12" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="533" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B533" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="534" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B534" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D534" s="14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="535" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B535" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D535" s="14" t="s">
         <v>13</v>
@@ -8964,12 +8965,12 @@
         <v>15</v>
       </c>
       <c r="L535" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="536" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B536" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L536" t="s">
         <v>26</v>
@@ -8980,7 +8981,7 @@
         <v>12</v>
       </c>
       <c r="B537" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D537" s="14" t="s">
         <v>13</v>
@@ -8991,37 +8992,37 @@
     </row>
     <row r="538" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A538" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B538" s="4" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D538" s="13" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F538" t="s">
         <v>15</v>
       </c>
       <c r="I538" s="9" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="L538" s="9" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="539" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A539" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B539" s="4"/>
       <c r="C539" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D539" s="13" t="s">
+        <v>651</v>
+      </c>
+      <c r="L539" s="9" t="s">
         <v>652</v>
-      </c>
-      <c r="L539" s="9" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="540" spans="1:12" x14ac:dyDescent="0.2">
@@ -9029,27 +9030,27 @@
         <v>12</v>
       </c>
       <c r="B540" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D540" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F540" t="s">
         <v>15</v>
       </c>
       <c r="I540" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="L540" s="9" t="s">
         <v>649</v>
-      </c>
-      <c r="L540" s="9" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="541" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A541" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B541" s="4" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D541" s="13"/>
       <c r="I541" s="9"/>
@@ -9060,19 +9061,19 @@
         <v>12</v>
       </c>
       <c r="B542" s="4" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F542" t="s">
         <v>15</v>
       </c>
       <c r="I542" s="9"/>
       <c r="L542" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="543" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B543" s="4" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="I543" s="9"/>
       <c r="L543" s="9"/>
@@ -9082,21 +9083,21 @@
         <v>12</v>
       </c>
       <c r="B544" s="4" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="I544" s="9"/>
       <c r="L544" s="9"/>
     </row>
     <row r="545" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B545" s="4" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="I545" s="9"/>
       <c r="L545" s="9"/>
     </row>
     <row r="546" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B546" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="I546" s="9"/>
       <c r="L546" s="9"/>
@@ -9112,7 +9113,7 @@
     </row>
     <row r="549" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L549" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Chapter/Chapter4.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167088A9-E3C7-4800-9CF3-60A0DC422503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15923BDB-99C8-4EF2-AF5B-B7075BEE73C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="剧情走向" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="748">
   <si>
     <t>人物</t>
   </si>
@@ -2813,10 +2813,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒_作战服|世界蛇成员 &gt;&gt; 淡出</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>wait &gt;&gt; 4|背景音乐进度 &gt;&gt; Hans Williamson - Cinematic Trailer &gt;&gt; 135</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -3362,6 +3358,18 @@
   </si>
   <si>
     <t>三人看见不远处有一个空心的光圈，那个光圈频繁抽搐，发射的光忽暗忽明。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>^漠寒_作战服|世界蛇成员 &gt;&gt; 淡入</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>^漠寒_作战服|世界蛇成员 &gt;&gt; 淡出</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>^漠寒_作战服|世界蛇成员</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -3882,7 +3890,7 @@
         <v>15</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -3902,7 +3910,7 @@
         <v>389</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D4" s="13"/>
     </row>
@@ -3911,7 +3919,7 @@
         <v>390</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D5" s="13"/>
     </row>
@@ -3920,7 +3928,7 @@
         <v>391</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D6" s="13"/>
     </row>
@@ -3929,7 +3937,7 @@
         <v>392</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D7" s="13"/>
     </row>
@@ -3938,7 +3946,7 @@
         <v>393</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D8" s="13"/>
     </row>
@@ -3947,16 +3955,16 @@
         <v>394</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B10" s="9" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>173</v>
@@ -3970,7 +3978,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>174</v>
@@ -4204,7 +4212,7 @@
         <v>12</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>405</v>
@@ -4307,7 +4315,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>408</v>
@@ -4348,7 +4356,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>51</v>
@@ -4385,7 +4393,7 @@
         <v>57</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F47" t="s">
         <v>15</v>
@@ -4435,7 +4443,7 @@
         <v>18</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
@@ -4443,7 +4451,7 @@
         <v>12</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
@@ -4451,7 +4459,7 @@
         <v>18</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
@@ -4459,7 +4467,7 @@
         <v>12</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>42</v>
@@ -4521,7 +4529,7 @@
         <v>12</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
@@ -4529,7 +4537,7 @@
         <v>18</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
@@ -4537,7 +4545,7 @@
         <v>311</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
@@ -4545,7 +4553,7 @@
         <v>205</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="L67" t="s">
         <v>69</v>
@@ -4565,7 +4573,7 @@
         <v>12</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I70" t="s">
         <v>70</v>
@@ -4576,7 +4584,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B71" s="9" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L71" t="s">
         <v>69</v>
@@ -4815,7 +4823,7 @@
         <v>22</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
@@ -4933,7 +4941,7 @@
         <v>12</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
@@ -4971,7 +4979,7 @@
         <v>207</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
@@ -5326,7 +5334,7 @@
         <v>422</v>
       </c>
       <c r="E154" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
@@ -5458,12 +5466,12 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B166" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B167" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
@@ -5471,7 +5479,7 @@
         <v>12</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
@@ -5487,7 +5495,7 @@
         <v>213</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
@@ -5511,7 +5519,7 @@
         <v>12</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
@@ -5538,7 +5546,7 @@
         <v>255</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
@@ -5549,7 +5557,7 @@
         <v>256</v>
       </c>
       <c r="C177" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
@@ -5557,7 +5565,7 @@
         <v>12</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C178" s="12" t="s">
         <v>227</v>
@@ -5577,7 +5585,7 @@
         <v>12</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
@@ -5585,7 +5593,7 @@
         <v>213</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
@@ -5593,7 +5601,7 @@
         <v>12</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
@@ -5601,7 +5609,7 @@
         <v>213</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
@@ -5609,7 +5617,7 @@
         <v>213</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
@@ -5617,7 +5625,7 @@
         <v>12</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
@@ -5625,7 +5633,7 @@
         <v>213</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
@@ -5633,7 +5641,7 @@
         <v>12</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C187" s="12" t="s">
         <v>406</v>
@@ -5737,7 +5745,7 @@
         <v>268</v>
       </c>
       <c r="C200" s="12" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.2">
@@ -5781,7 +5789,7 @@
     <row r="205" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A205" s="11"/>
       <c r="B205" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C205" s="11" t="s">
         <v>276</v>
@@ -5808,7 +5816,7 @@
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A208" s="11"/>
       <c r="B208" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C208" s="11" t="s">
         <v>276</v>
@@ -5866,7 +5874,7 @@
         <v>205</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
@@ -5874,7 +5882,7 @@
         <v>12</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
@@ -5882,7 +5890,7 @@
         <v>19</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.2">
@@ -5906,7 +5914,7 @@
         <v>12</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -5914,7 +5922,7 @@
         <v>19</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
@@ -5930,7 +5938,7 @@
         <v>22</v>
       </c>
       <c r="B222" s="8" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.2">
@@ -5946,7 +5954,7 @@
         <v>19</v>
       </c>
       <c r="B224" s="8" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.2">
@@ -5995,7 +6003,7 @@
         <v>218</v>
       </c>
       <c r="E229" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.2">
@@ -6009,7 +6017,7 @@
         <v>13</v>
       </c>
       <c r="E230" s="12" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F230" t="s">
         <v>15</v>
@@ -6020,33 +6028,33 @@
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B231" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E231" s="12" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B232" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E232" s="12"/>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B233" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E233" s="12"/>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B234" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E234" s="12"/>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B235" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E235" s="12"/>
     </row>
@@ -6102,7 +6110,7 @@
         <v>18</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.2">
@@ -6110,7 +6118,7 @@
         <v>22</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.2">
@@ -6118,7 +6126,7 @@
         <v>19</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.2">
@@ -6126,12 +6134,12 @@
         <v>12</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B244" s="4" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.2">
@@ -6239,7 +6247,7 @@
         <v>111</v>
       </c>
       <c r="E256" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.2">
@@ -6253,7 +6261,7 @@
         <v>388</v>
       </c>
       <c r="E257" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F257" s="9" t="s">
         <v>350</v>
@@ -6342,7 +6350,7 @@
         <v>429</v>
       </c>
       <c r="L267" s="9" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.2">
@@ -6376,13 +6384,13 @@
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B272" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G272" t="s">
         <v>118</v>
       </c>
       <c r="L272" s="9" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.2">
@@ -6484,7 +6492,7 @@
         <v>12</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C284" s="12" t="s">
         <v>216</v>
@@ -6509,7 +6517,7 @@
         <v>12</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C286" s="12" t="s">
         <v>437</v>
@@ -6543,7 +6551,7 @@
         <v>12</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C289" s="12"/>
     </row>
@@ -6582,7 +6590,7 @@
         <v>19</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.2">
@@ -6590,7 +6598,7 @@
         <v>197</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.2">
@@ -6598,7 +6606,7 @@
         <v>19</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.2">
@@ -6606,7 +6614,7 @@
         <v>12</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.2">
@@ -6614,7 +6622,7 @@
         <v>19</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.2">
@@ -6622,7 +6630,7 @@
         <v>12</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C298" s="10" t="s">
         <v>50</v>
@@ -6633,7 +6641,7 @@
         <v>19</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.2">
@@ -6649,12 +6657,12 @@
         <v>12</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B302" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C302" s="10" t="s">
         <v>122</v>
@@ -6668,7 +6676,7 @@
         <v>388</v>
       </c>
       <c r="E303" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.2">
@@ -6676,7 +6684,7 @@
         <v>12</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C304" s="10" t="s">
         <v>123</v>
@@ -6685,7 +6693,7 @@
         <v>124</v>
       </c>
       <c r="E304" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F304" t="s">
         <v>15</v>
@@ -6696,7 +6704,7 @@
         <v>311</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.2">
@@ -6704,7 +6712,7 @@
         <v>19</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.2">
@@ -6712,12 +6720,12 @@
         <v>12</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B308" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C308" s="10" t="s">
         <v>122</v>
@@ -6726,7 +6734,7 @@
         <v>125</v>
       </c>
       <c r="E308" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F308" t="s">
         <v>17</v>
@@ -6773,7 +6781,7 @@
         <v>125</v>
       </c>
       <c r="E313" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="I313" t="s">
         <v>131</v>
@@ -6784,7 +6792,7 @@
         <v>320</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C314" s="3" t="s">
         <v>106</v>
@@ -6793,7 +6801,7 @@
         <v>132</v>
       </c>
       <c r="E314" s="12" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F314" t="s">
         <v>15</v>
@@ -6802,28 +6810,28 @@
     <row r="315" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A315" s="11"/>
       <c r="B315" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C315" s="3"/>
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A316" s="11"/>
       <c r="B316" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C316" s="3"/>
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A317" s="11"/>
       <c r="B317" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C317" s="3"/>
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A318" s="11"/>
       <c r="B318" s="4" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C318" s="3"/>
     </row>
@@ -6832,14 +6840,14 @@
         <v>320</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C319" s="3"/>
       <c r="D319" s="14" t="s">
         <v>132</v>
       </c>
       <c r="E319" s="12" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.2">
@@ -6853,7 +6861,7 @@
         <v>125</v>
       </c>
       <c r="E320" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F320" t="s">
         <v>15</v>
@@ -6861,7 +6869,7 @@
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B321" s="4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C321" s="10" t="s">
         <v>134</v>
@@ -6874,33 +6882,33 @@
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B323" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B324" s="4" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B325" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B326" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B327" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D327" s="13" t="s">
         <v>499</v>
       </c>
       <c r="E327" s="12" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.2">
@@ -6908,13 +6916,13 @@
         <v>12</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D328" s="13" t="s">
         <v>388</v>
       </c>
       <c r="E328" s="12" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="329" spans="1:12" x14ac:dyDescent="0.2">
@@ -6922,7 +6930,7 @@
         <v>12</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D329" s="13"/>
       <c r="E329" s="12"/>
@@ -6932,7 +6940,7 @@
         <v>12</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C330" s="12" t="s">
         <v>500</v>
@@ -6951,7 +6959,7 @@
         <v>135</v>
       </c>
       <c r="E331" s="12" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="F331" t="s">
         <v>15</v>
@@ -6970,7 +6978,7 @@
         <v>136</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C333" s="10" t="s">
         <v>106</v>
@@ -7004,7 +7012,7 @@
         <v>112</v>
       </c>
       <c r="L336" s="9" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.2">
@@ -7039,7 +7047,7 @@
         <v>142</v>
       </c>
       <c r="E340" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.2">
@@ -7056,7 +7064,7 @@
         <v>135</v>
       </c>
       <c r="E341" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="L341" s="9" t="s">
         <v>549</v>
@@ -7285,7 +7293,7 @@
         <v>12</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D365" s="13"/>
       <c r="F365" s="9"/>
@@ -7395,7 +7403,7 @@
         <v>12</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.2">
@@ -7403,7 +7411,7 @@
         <v>12</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.2">
@@ -7566,7 +7574,7 @@
         <v>441</v>
       </c>
       <c r="E398" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.2">
@@ -7585,7 +7593,7 @@
         <v>22</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E400" s="10" t="s">
         <v>153</v>
@@ -7643,7 +7651,7 @@
         <v>173</v>
       </c>
       <c r="E405" s="12" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="406" spans="1:12" x14ac:dyDescent="0.2">
@@ -7669,16 +7677,16 @@
         <v>12</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D408" s="13" t="s">
         <v>445</v>
       </c>
       <c r="I408" s="9" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="L408" s="9" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="409" spans="1:12" x14ac:dyDescent="0.2">
@@ -7690,10 +7698,10 @@
         <v>450</v>
       </c>
       <c r="D409" s="12" t="s">
+        <v>640</v>
+      </c>
+      <c r="L409" s="9" t="s">
         <v>641</v>
-      </c>
-      <c r="L409" s="9" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="410" spans="1:12" x14ac:dyDescent="0.2">
@@ -7710,10 +7718,10 @@
         <v>445</v>
       </c>
       <c r="I410" s="9" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="L410" s="9" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="411" spans="1:12" x14ac:dyDescent="0.2">
@@ -7860,7 +7868,7 @@
     </row>
     <row r="426" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B426" s="4" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="427" spans="1:12" x14ac:dyDescent="0.2">
@@ -7876,13 +7884,13 @@
         <v>348</v>
       </c>
       <c r="C428" s="12" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D428" s="13" t="s">
         <v>349</v>
       </c>
       <c r="E428" s="12" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F428" s="9" t="s">
         <v>351</v>
@@ -7902,7 +7910,7 @@
         <v>383</v>
       </c>
       <c r="E429" s="12" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F429" s="9" t="s">
         <v>351</v>
@@ -8011,7 +8019,7 @@
         <v>353</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C440" s="10" t="s">
         <v>106</v>
@@ -8082,6 +8090,9 @@
       <c r="C446" s="10" t="s">
         <v>104</v>
       </c>
+      <c r="G446" s="9" t="s">
+        <v>606</v>
+      </c>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A447" s="3" t="s">
@@ -8090,6 +8101,9 @@
       <c r="B447" s="4" t="s">
         <v>359</v>
       </c>
+      <c r="G447" s="9" t="s">
+        <v>747</v>
+      </c>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A448" s="3" t="s">
@@ -8222,7 +8236,7 @@
         <v>369</v>
       </c>
       <c r="G463" s="9" t="s">
-        <v>606</v>
+        <v>745</v>
       </c>
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.2">
@@ -8233,7 +8247,7 @@
         <v>370</v>
       </c>
       <c r="G464" s="9" t="s">
-        <v>607</v>
+        <v>746</v>
       </c>
     </row>
     <row r="465" spans="1:12" x14ac:dyDescent="0.2">
@@ -8252,7 +8266,7 @@
         <v>372</v>
       </c>
       <c r="G466" s="9" t="s">
-        <v>607</v>
+        <v>746</v>
       </c>
     </row>
     <row r="467" spans="1:12" x14ac:dyDescent="0.2">
@@ -8266,7 +8280,7 @@
         <v>461</v>
       </c>
       <c r="G467" s="9" t="s">
-        <v>606</v>
+        <v>745</v>
       </c>
     </row>
     <row r="468" spans="1:12" x14ac:dyDescent="0.2">
@@ -8288,7 +8302,7 @@
         <v>383</v>
       </c>
       <c r="G469" s="9" t="s">
-        <v>606</v>
+        <v>745</v>
       </c>
     </row>
     <row r="470" spans="1:12" x14ac:dyDescent="0.2">
@@ -8322,10 +8336,10 @@
         <v>383</v>
       </c>
       <c r="E471" s="12" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G471" s="9" t="s">
-        <v>606</v>
+        <v>745</v>
       </c>
     </row>
     <row r="472" spans="1:12" x14ac:dyDescent="0.2">
@@ -8519,7 +8533,7 @@
         <v>205</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="L491" s="9"/>
     </row>
@@ -8537,7 +8551,7 @@
         <v>19</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="L493" s="9"/>
     </row>
@@ -8623,7 +8637,7 @@
     </row>
     <row r="503" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B503" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L503" s="9"/>
     </row>
@@ -8927,7 +8941,7 @@
         <v>12</v>
       </c>
       <c r="B531" s="4" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C531" s="12" t="s">
         <v>216</v>
@@ -8935,7 +8949,7 @@
     </row>
     <row r="532" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B532" s="4" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C532" s="12" t="s">
         <v>406</v>
@@ -8943,12 +8957,12 @@
     </row>
     <row r="533" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B533" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="534" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B534" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D534" s="14" t="s">
         <v>170</v>
@@ -8981,7 +8995,7 @@
         <v>12</v>
       </c>
       <c r="B537" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D537" s="14" t="s">
         <v>13</v>
@@ -8995,19 +9009,19 @@
         <v>115</v>
       </c>
       <c r="B538" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D538" s="13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F538" t="s">
         <v>15</v>
       </c>
       <c r="I538" s="9" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="L538" s="9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="539" spans="1:12" x14ac:dyDescent="0.2">
@@ -9019,10 +9033,10 @@
         <v>166</v>
       </c>
       <c r="D539" s="13" t="s">
+        <v>650</v>
+      </c>
+      <c r="L539" s="9" t="s">
         <v>651</v>
-      </c>
-      <c r="L539" s="9" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="540" spans="1:12" x14ac:dyDescent="0.2">
@@ -9030,7 +9044,7 @@
         <v>12</v>
       </c>
       <c r="B540" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D540" s="13" t="s">
         <v>173</v>
@@ -9039,10 +9053,10 @@
         <v>15</v>
       </c>
       <c r="I540" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="L540" s="9" t="s">
         <v>648</v>
-      </c>
-      <c r="L540" s="9" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="541" spans="1:12" x14ac:dyDescent="0.2">
@@ -9050,7 +9064,7 @@
         <v>115</v>
       </c>
       <c r="B541" s="4" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D541" s="13"/>
       <c r="I541" s="9"/>
@@ -9061,7 +9075,7 @@
         <v>12</v>
       </c>
       <c r="B542" s="4" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F542" t="s">
         <v>15</v>
@@ -9073,7 +9087,7 @@
     </row>
     <row r="543" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B543" s="4" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="I543" s="9"/>
       <c r="L543" s="9"/>
@@ -9083,14 +9097,14 @@
         <v>12</v>
       </c>
       <c r="B544" s="4" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="I544" s="9"/>
       <c r="L544" s="9"/>
     </row>
     <row r="545" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B545" s="4" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="I545" s="9"/>
       <c r="L545" s="9"/>
